--- a/naver-place-crawler/results_nail/사상구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/사상구_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V116"/>
+  <dimension ref="A1:V117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일애 푸스케어 부산엄궁점</t>
+          <t>썬뷰티네일샵</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fusscare_nailaee@naver.com</t>
+          <t>artst_snu@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1379-0163</t>
+          <t>0507-1375-2696</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 144 1층 105호</t>
+          <t>부산광역시 사상구 백양대로342번길 21 206호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.aee</t>
+          <t>https://www.instagram.com/sunnailshop2696</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>156</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1438869369</t>
+          <t>1498701306</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438869369</t>
+          <t>https://m.place.naver.com/place/1498701306</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨네일</t>
+          <t>꿈꾸는네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ansh1128@naver.com</t>
+          <t>dreamnail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1382-8160</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 733 롯데마트 사상점 3층</t>
+          <t>부산광역시 사상구 엄궁로179번길 9-8 꿈꾸는네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/cnail_3</t>
+          <t>https://www.instagram.com/the_dream.nail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16801995</t>
+          <t>1792266910</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16801995</t>
+          <t>https://m.place.naver.com/place/1792266910</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일하루 사상본점</t>
+          <t>지니네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nolmukzzang@naver.com</t>
+          <t>goto_seoul@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1311-3336</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 214 3층 네일하루</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자상가 2층 273호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailharu3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +776,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>758</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>829</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1328657179</t>
+          <t>31505917</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328657179</t>
+          <t>https://m.place.naver.com/place/31505917</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일더끌림</t>
+          <t>마녀손톱</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rktngpfud@naver.com</t>
+          <t>vitaminiya@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>051-977-0977</t>
+          <t>051-311-2204</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 47 네일더끌림</t>
+          <t>부산광역시 사상구 백양대로494번길 19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rktngpfud</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +870,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1805551094</t>
+          <t>1020368554</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805551094</t>
+          <t>https://m.place.naver.com/place/1020368554</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일제이</t>
+          <t>네일애 푸스케어 부산엄궁점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jiwon3716@naver.com</t>
+          <t>fusscare_nailaee@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1308-3976</t>
+          <t>0507-1379-0163</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 326 1층 네일제이</t>
+          <t>부산광역시 사상구 엄궁로 144 1층 105호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiwon3716</t>
+          <t>https://www.instagram.com/nail.aee</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="R6" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1944314268</t>
+          <t>1438869369</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944314268</t>
+          <t>https://m.place.naver.com/place/1438869369</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,35 +1026,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일미</t>
+          <t>썬네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>041nail@naver.com</t>
+          <t>sunnail3024@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1356-6980</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모덕로 32</t>
+          <t>부산광역시 사상구 광장로 7 1층 1번가 1337,1338호(괘법동, 르네시떼)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://zero.gongbiz.kr/shop/S000016770</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1083,17 +1079,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1163149926</t>
+          <t>1046901734</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163149926</t>
+          <t>https://m.place.naver.com/place/1046901734</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,25 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>무이네일</t>
+          <t>쏭네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>baeyou0417@naver.com</t>
+          <t>ssongnail01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1372-6483</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 21 1층 (부산광역시 사상구 삼락동 418-8 1층)</t>
+          <t>부산광역시 사상구 낙동대로776번길 36 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooinail_uz</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1347978558</t>
+          <t>1484173928</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347978558</t>
+          <t>https://m.place.naver.com/place/1484173928</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일1one</t>
+          <t>네일제이</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>high0902@naver.com</t>
+          <t>jiwon3716@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1371-1157</t>
+          <t>0507-1308-3976</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로1210번길 50 상가 동원부동산옆</t>
+          <t>부산광역시 사상구 백양대로 326 1층 네일제이</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail1one</t>
+          <t>https://blog.naver.com/jiwon3716</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1150830105</t>
+          <t>1944314268</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150830105</t>
+          <t>https://m.place.naver.com/place/1944314268</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>꿈꾸는네일</t>
+          <t>케이뷰티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dreamnail@naver.com</t>
+          <t>bi1142@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>051-669-6355</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번길 9-8 꿈꾸는네일</t>
+          <t>부산광역시 사상구 낙동대로 910</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_dream.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1336,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1357,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1792266910</t>
+          <t>1104145262</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792266910</t>
+          <t>https://m.place.naver.com/place/1104145262</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1398,29 +1402,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>준,네일</t>
+          <t>모라네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>luv0e@naver.com</t>
+          <t>jessicanail@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1353-4384</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁남로11번길 16 1층</t>
+          <t>부산광역시 사상구 모라로51번길 16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/june__nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1490919782</t>
+          <t>2143022752</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490919782</t>
+          <t>https://m.place.naver.com/place/2143022752</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1492,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아이리스네일</t>
+          <t>지혜네일샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kitty666@naver.com</t>
+          <t>liz_kang@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>051-319-5413</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1413호</t>
+          <t>부산광역시 사상구 삼덕로46번안길 28 조선사</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kitty666</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,12 +1520,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>35228104</t>
+          <t>1658577122</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35228104</t>
+          <t>https://m.place.naver.com/place/1658577122</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>쏭네일</t>
+          <t>네일로움 &amp; 속눈썹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ssongnail01@naver.com</t>
+          <t>vjkzmf10@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1355-9745</t>
+          <t>0507-1370-0917</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 양지로24번길 2 1층 쏭네일</t>
+          <t>부산광역시 사상구 운산로 36 한신아파트1차 상가 2층 네일로움</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nailroum_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1618,7 +1614,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1639,17 +1635,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>301</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>546</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1669157044</t>
+          <t>1187665708</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669157044</t>
+          <t>https://m.place.naver.com/place/1187665708</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1676,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>하이네일</t>
+          <t>다온네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>freegirl11@naver.com</t>
+          <t>daonnail7001@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1308-0940</t>
+          <t>0507-1411-4369</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로342번길 21 벽산늘푸른상가 2층</t>
+          <t>부산광역시 사상구 대동로 100 2층 다온네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hi_nailll</t>
+          <t>https://instagram.com/daonnail_eyelash?igshid=17rcqxfqkj24i</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1740,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1748,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1223881417</t>
+          <t>773488991</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223881417</t>
+          <t>https://m.place.naver.com/place/773488991</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1770,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>마녀손톱</t>
+          <t>초록뷰티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vitaminiya@naver.com</t>
+          <t>8852561@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>051-311-2204</t>
+          <t>0507-1496-1644</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로494번길 19</t>
+          <t>부산광역시 사상구 백양대로 883 상가 10동 2층 206호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/chorok__beauty?igsh=Zm1vNDRnNHRueXJ6&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1806,7 +1802,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1827,17 +1823,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1020368554</t>
+          <t>1679896666</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1020368554</t>
+          <t>https://m.place.naver.com/place/1679896666</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1877,16 +1873,20 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1379-0989</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로51번길 16</t>
+          <t>부산광역시 사상구 모라로51번길 16 1층(모라네일)/구 헤이진 네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/heyjin2019</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1917,17 +1917,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1936,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2143022752</t>
+          <t>1537116650</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2143022752</t>
+          <t>https://m.place.naver.com/place/1537116650</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1958,29 +1958,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일로움 &amp; 속눈썹</t>
+          <t>제이뷰티</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>vjkzmf10@naver.com</t>
+          <t>ggaau0073@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1370-0917</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 36 한신아파트1차 상가 2층 네일로움</t>
+          <t>부산광역시 사상구 광장로 91 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailroum_</t>
+          <t>https://www.instagram.com/jbeauty_nailsalon?igsh=NG5ubXc0MjdocWMx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2015,13 +2011,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>545</v>
+        <v>3</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1187665708</t>
+          <t>2006084959</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187665708</t>
+          <t>https://m.place.naver.com/place/2006084959</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2048,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>두손네일</t>
+          <t>수아한네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>doosonnail@naver.com</t>
+          <t>ksh_6563@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1345-9948</t>
+          <t>0507-1441-0277</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 8 두손네일</t>
+          <t>부산광역시 사상구 대동로 94 2층 248호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/doson_nail_jina</t>
+          <t>https://www.instagram.com/suahan_nail?igsh=MTZnYnRmNmFnNTQ4MA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,13 +2105,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1568106556</t>
+          <t>1798118492</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568106556</t>
+          <t>https://m.place.naver.com/place/1798118492</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2146,34 +2142,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>늘예쁨 네일</t>
+          <t>예블링네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>thsghkwlsas@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1356-6612</t>
+          <t>0507-1462-0158</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 369 1층</t>
+          <t>부산광역시 사상구 덕상로 19-1 1층 예블링네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlQmxnn</t>
+          <t>https://www.instagram.com/yebling_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2194,7 +2190,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2203,13 +2199,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2214,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2079016042</t>
+          <t>1115413707</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079016042</t>
+          <t>https://m.place.naver.com/place/1115413707</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2236,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>샤네일</t>
+          <t>홍네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wood1030@naver.com</t>
+          <t>6569807@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1313-5869</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자상가 1층114호</t>
+          <t>부산광역시 사상구 사상로309번길 49</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wood1030</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2272,12 +2264,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2293,18 +2285,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>22</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2312,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>33399488</t>
+          <t>1603273526</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33399488</t>
+          <t>https://m.place.naver.com/place/1603273526</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2326,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>쏭네일</t>
+          <t>빛날희네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ssongnail01@naver.com</t>
+          <t>kimmihee4@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1372-6483</t>
+          <t>0507-1358-0304</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로776번길 36 1층</t>
+          <t>부산광역시 사상구 광장로104번길 27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heenail03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,7 +2358,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2387,17 +2379,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1484173928</t>
+          <t>1358743723</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484173928</t>
+          <t>https://m.place.naver.com/place/1358743723</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2420,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일더예쁜눈</t>
+          <t>준,네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>noblelizent@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1348-1127</t>
+          <t>0507-1353-4384</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로366번길 56 2층 네일더예쁜눈</t>
+          <t>부산광역시 사상구 엄궁남로11번길 16 1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://naileye.itpage.kr</t>
+          <t>https://www.instagram.com/june__nail_/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2477,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="R22" t="n">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2492,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1141282133</t>
+          <t>1490919782</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141282133</t>
+          <t>https://m.place.naver.com/place/1490919782</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2522,34 +2514,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>라움네일</t>
+          <t>눈부시네.일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>brcomm0371@naver.com</t>
+          <t>happygirlmh@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1361-9872</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 166 리치플러스아파트 상가동 102호</t>
+          <t>부산광역시 사상구 주례로9번길 3 눈부시네.일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss-order.tossplace.com/booking/N2L40xfR9x2ivsY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2575,17 +2563,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1322569547</t>
+          <t>2145722253</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322569547</t>
+          <t>https://m.place.naver.com/place/2145722253</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2616,25 +2604,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>클라라네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hackerstalk11@naver.com</t>
+          <t>laura1016@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1352-5400</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁북로 59 롯데캐슬리버 401동앞 상가1층</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1401호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thumb__nail__?igshid=16cyosojl8iua</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2644,7 +2636,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2665,17 +2657,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="R24" t="n">
-        <v>11</v>
+        <v>352</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2676,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1022811581</t>
+          <t>37638497</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022811581</t>
+          <t>https://m.place.naver.com/place/37638497</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2706,29 +2698,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일&amp;풋</t>
+          <t>네리나네일앤뷰티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>algid1235@naver.com</t>
+          <t>kjinsook2004@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1479-7850</t>
+          <t>0507-1428-1560</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 76 상가동 1층 104호</t>
+          <t>부산광역시 사상구 강선로 18 1층 네리나 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.and.foot</t>
+          <t>https://www.instagram.com/nerina_nail?igsh=MXhiZ296NXdneXcw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2763,10 +2755,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>113</v>
@@ -2778,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1395529953</t>
+          <t>1273947079</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395529953</t>
+          <t>https://m.place.naver.com/place/1273947079</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2800,34 +2792,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일이지</t>
+          <t>오브네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>easynailgainmiga@naver.com</t>
+          <t>ofrang@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1390-3978</t>
+          <t>0507-1370-9776</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번가길 17-9 1층</t>
+          <t>부산광역시 사상구 가야대로366번길 19 . 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_2ji</t>
+          <t>http://pf.kakao.com/_gxixiTG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2848,7 +2840,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2857,13 +2849,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2864,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2022406101</t>
+          <t>1071928305</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022406101</t>
+          <t>https://m.place.naver.com/place/1071928305</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2894,25 +2886,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일포레</t>
+          <t>두손네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nail_foret@naver.com</t>
+          <t>doosonnail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1345-9948</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로90번길 6 1층 왼쪽</t>
+          <t>부산광역시 사상구 사상로238번길 8 두손네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_for.et?igsh=Zjk2cnE5emQ4MDR1&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/doson_nail_jina</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2947,13 +2943,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2958,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2032419101</t>
+          <t>1568106556</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032419101</t>
+          <t>https://m.place.naver.com/place/1568106556</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2984,34 +2980,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>라비앙로즈네일</t>
+          <t>네일해찌</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wlsthf1d1@naver.com</t>
+          <t>archive_olivia@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1340-8327</t>
+          <t>0507-1347-0019</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 288 창조센츄리 상가 2층</t>
+          <t>부산광역시 사상구 사상로 172 A동 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_CZBEs</t>
+          <t>https://www.instagram.com/nailhaejji_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3032,7 +3028,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3041,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="R28" t="n">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1335031344</t>
+          <t>1433672492</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335031344</t>
+          <t>https://m.place.naver.com/place/1433672492</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3078,29 +3074,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>달처럼예뻐라</t>
+          <t>핑크네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>haru_04@naver.com</t>
+          <t>go8282c@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1494-2578</t>
+          <t>0507-1334-0020</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 28 상가13동 2층 205호</t>
+          <t>부산광역시 사상구 주례로 15 3층 핑크네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pinknail_busan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3110,7 +3106,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3131,17 +3127,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="R29" t="n">
-        <v>67</v>
+        <v>347</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1699052156</t>
+          <t>36924982</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699052156</t>
+          <t>https://m.place.naver.com/place/36924982</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3172,24 +3168,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>야시 속눈썹&amp;네일</t>
+          <t>유네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nice0304011@naver.com</t>
+          <t>luvu1016@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1303-4262</t>
+          <t>0507-1399-0460</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 484 1층 야시속눈썹</t>
+          <t>부산광역시 사상구 대동로 94 상가동 2층 282호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3229,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1656610719</t>
+          <t>1060258369</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656610719</t>
+          <t>https://m.place.naver.com/place/1060258369</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3262,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일마루&amp;카페</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>suji6777@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1321-4724</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 372-22 반도보라메머드타운상가 209호</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼시떼관 1층 1396,1405호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailmaru</t>
+          <t>http://instagram.com/the_nail_sasang</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3315,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3330,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1730313997</t>
+          <t>1179834131</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730313997</t>
+          <t>https://m.place.naver.com/place/1179834131</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3352,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>샛별네일아트</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3373,12 +3365,12 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼시떼관 1층 1396,1405호</t>
+          <t>부산광역시 사상구 대동로 94 2동 236호 (학장동,반도프라자)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_nail_sasang</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3388,7 +3380,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3409,17 +3401,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3420,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1179834131</t>
+          <t>1396422090</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179834131</t>
+          <t>https://m.place.naver.com/place/1396422090</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3450,29 +3442,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일파크</t>
+          <t>힐링네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>eunmijan@naver.com</t>
+          <t>lovekeiti@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1441-4147</t>
+          <t>0507-1423-9082</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로360번길 1 2층</t>
+          <t>부산광역시 사상구 가야대로 384 1층 네일샵</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailpark</t>
+          <t>https://www.instagram.com/_healing_nail_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3507,13 +3499,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3514,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1218794769</t>
+          <t>2067519657</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218794769</t>
+          <t>https://m.place.naver.com/place/2067519657</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3544,24 +3536,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>루미아 네일 뷰티케어</t>
+          <t>네일톡톡</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shinakari@naver.com</t>
+          <t>ekgnlzz@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1345-8988</t>
+          <t>0507-1333-0960</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로907번가길 54 1층</t>
+          <t>부산광역시 사상구 낙동대로1210번길 78 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3601,13 +3593,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3608,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2095013714</t>
+          <t>1484262326</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095013714</t>
+          <t>https://m.place.naver.com/place/1484262326</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3638,24 +3630,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일공간</t>
+          <t>네일미</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gol2006@naver.com</t>
+          <t>041nail@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>051-319-5340</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1339-1340호</t>
+          <t>부산광역시 사상구 모덕로 32</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3695,13 +3683,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3698,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>34283776</t>
+          <t>1163149926</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34283776</t>
+          <t>https://m.place.naver.com/place/1163149926</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3732,29 +3720,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>단미뷰티</t>
+          <t>네일공간</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kmlove123@naver.com</t>
+          <t>gol2006@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1390-0815</t>
+          <t>051-319-5340</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로110번길 5 2층</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1339-1340호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danmi__bt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3764,7 +3752,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3785,17 +3773,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3792,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1759913260</t>
+          <t>34283776</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759913260</t>
+          <t>https://m.place.naver.com/place/34283776</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3826,29 +3814,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네리나네일앤뷰티</t>
+          <t>네일1one</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kjinsook2004@naver.com</t>
+          <t>high0902@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1428-1560</t>
+          <t>0507-1371-1157</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 강선로 18 1층 네리나 네일&amp;뷰티</t>
+          <t>부산광역시 사상구 낙동대로1210번길 50 상가 동원부동산옆</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nerina_nail?igsh=MXhiZ296NXdneXcw&amp;utm_source=qr</t>
+          <t>http://instagram.com/nail1one</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3883,13 +3871,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,17 +3886,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1273947079</t>
+          <t>1150830105</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273947079</t>
+          <t>https://m.place.naver.com/place/1150830105</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3931,18 +3919,18 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1309-0526</t>
+          <t>0507-1406-7510</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번길 21 3층 주네일</t>
+          <t>부산광역시 사상구 사상로238번길 28 1층 주네일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/joonail623</t>
+          <t>https://www.instagram.com/7junail7</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3977,13 +3965,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,17 +3980,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1588835862</t>
+          <t>1705139517</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588835862</t>
+          <t>https://m.place.naver.com/place/1705139517</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4014,29 +4002,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>퀸즈네일</t>
+          <t>미유네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>qu_eenz@naver.com</t>
+          <t>atsing427@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>051-322-1145</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 괘감로 97</t>
+          <t>부산광역시 사상구 사상로233번길 14 1층 102호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/stxAgifc</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4046,7 +4030,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4062,22 +4046,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4070,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>21505702</t>
+          <t>2007447861</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21505702</t>
+          <t>https://m.place.naver.com/place/2007447861</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4108,29 +4092,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일k</t>
+          <t>네일더예쁜눈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>oio7845@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1313-2205</t>
+          <t>0507-1348-1127</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 490 주례1차동일아파트 106동 1층 107-2호</t>
+          <t>부산광역시 사상구 가야대로366번길 56 2층 네일더예쁜눈</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://naileye.itpage.kr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4140,7 +4124,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4161,17 +4145,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4164,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1029204849</t>
+          <t>1141282133</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1029204849</t>
+          <t>https://m.place.naver.com/place/1141282133</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4202,24 +4186,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOAS</t>
+          <t>라움네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shintc@naver.com</t>
+          <t>realbarbie77@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>051-325-9903</t>
+          <t>0507-1361-9872</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 22</t>
+          <t>부산광역시 사상구 사상로 166 리치플러스아파트 상가동 102호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4259,13 +4243,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,17 +4258,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1997973035</t>
+          <t>1322569547</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997973035</t>
+          <t>https://m.place.naver.com/place/1322569547</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4296,29 +4280,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일하이디</t>
+          <t>요술손</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>smwls0114@naver.com</t>
+          <t>yosulson_party@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1341-4976</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로504번길 2 1층</t>
+          <t>부산광역시 사상구 사상로250번길 22</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hi.d</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4328,7 +4308,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4349,17 +4329,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,17 +4348,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1061733115</t>
+          <t>1330709122</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061733115</t>
+          <t>https://m.place.naver.com/place/1330709122</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4390,29 +4370,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일도로시</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>whektha1613@naver.com</t>
-        </is>
-      </c>
+          <t>pickynail</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1316-9113</t>
+          <t>0507-1333-5263</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로203번길 38 1층</t>
+          <t>부산광역시 사상구 사상로223번길 23 303동 102호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://instagram.com/_nail_dorothy_?igshid=irihcx1mq6ow</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4422,7 +4398,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4443,17 +4419,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,17 +4438,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1033126412</t>
+          <t>2053102298</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033126412</t>
+          <t>https://m.place.naver.com/place/2053102298</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4484,29 +4460,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일더드림</t>
+          <t>하얀네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rabbit0577@naver.com</t>
+          <t>whitenail27@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>051-323-0807</t>
+          <t>0507-1490-1110</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 195</t>
+          <t>부산광역시 사상구 동주로 24 1층 하얀네일</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thedream/</t>
+          <t>http://instagram.com/hayan_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4541,13 +4517,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R44" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4532,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>517958118</t>
+          <t>1581947459</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/517958118</t>
+          <t>https://m.place.naver.com/place/1581947459</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4578,29 +4554,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일해찌</t>
+          <t>네일도설렘 부산점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>archive_olivia@naver.com</t>
+          <t>pongx22@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1347-0019</t>
+          <t>0507-1375-6752</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 172 A동 1층</t>
+          <t>부산광역시 사상구 사상로 248 2층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhaejji_</t>
+          <t>https://www.instagram.com/sun.young218700</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4635,13 +4611,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>391</v>
+        <v>26</v>
       </c>
       <c r="Q45" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>432</v>
+        <v>28</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4626,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1433672492</t>
+          <t>1809754813</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433672492</t>
+          <t>https://m.place.naver.com/place/1809754813</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4672,29 +4648,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>힐링네일</t>
+          <t>네일&amp;풋</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>lovekeiti@naver.com</t>
+          <t>algid1235@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1423-9082</t>
+          <t>0507-1479-7850</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 384 1층 네일샵</t>
+          <t>부산광역시 사상구 대동로 76 상가동 1층 104호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_healing_nail_</t>
+          <t>https://www.instagram.com/nail.and.foot</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4729,13 +4705,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4720,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2067519657</t>
+          <t>1395529953</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067519657</t>
+          <t>https://m.place.naver.com/place/1395529953</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4766,29 +4742,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>다온네일</t>
+          <t>용이뷰티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>daonnail7001@naver.com</t>
+          <t>yurim012@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1411-4369</t>
+          <t>0507-1406-6990</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 100 2층 다온네일</t>
+          <t>부산광역시 사상구 백양대로 950</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://instagram.com/daonnail_eyelash?igshid=17rcqxfqkj24i</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4798,7 +4774,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4819,17 +4795,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4838,17 +4814,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>773488991</t>
+          <t>38521099</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/773488991</t>
+          <t>https://m.place.naver.com/place/38521099</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4860,29 +4836,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HERO 네일</t>
+          <t>퀸네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hero_0304@naver.com</t>
+          <t>miinijk@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1368-2076</t>
+          <t>0507-1380-2805</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 760 1층</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자 1층 110호 퀸네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hero_nail_1101</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4892,7 +4868,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4913,17 +4889,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4932,17 +4908,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1884120549</t>
+          <t>1679312982</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884120549</t>
+          <t>https://m.place.naver.com/place/1679312982</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4954,29 +4930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일도설렘 부산점</t>
+          <t>네일콩</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pongx22@naver.com</t>
+          <t>besmlsk@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1375-6752</t>
+          <t>0507-1306-3190</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 248 2층</t>
+          <t>부산광역시 사상구 덕상로 10 오양상가 303호 네일콩</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sun.young218700</t>
+          <t>https://www.instagram.com/nailkong.k</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5011,13 +4987,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5026,17 +5002,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1809754813</t>
+          <t>1444223522</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809754813</t>
+          <t>https://m.place.naver.com/place/1444223522</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5048,29 +5024,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>썬뷰티네일샵</t>
+          <t>샤네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>artst_snu@naver.com</t>
+          <t>wood1030@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1375-2696</t>
+          <t>0507-1313-5869</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로342번길 21 206호</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자상가 1층114호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunnailshop2696</t>
+          <t>https://blog.naver.com/wood1030</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5085,7 +5061,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5105,13 +5081,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5120,17 +5096,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1498701306</t>
+          <t>33399488</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498701306</t>
+          <t>https://m.place.naver.com/place/33399488</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5142,29 +5118,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>로코네일</t>
+          <t>네일하루 사상본점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>u_love118@naver.com</t>
+          <t>nolmukzzang@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1391-7108</t>
+          <t>0507-1311-3336</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 5 . 1층 루니움뷰티&amp;케어</t>
+          <t>부산광역시 사상구 사상로 214 3층 네일하루</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_loconail</t>
+          <t>http://www.instagram.com/nailharu3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5190,7 +5166,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5199,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>257</v>
+        <v>760</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="R51" t="n">
-        <v>274</v>
+        <v>831</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5214,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1303113106</t>
+          <t>1328657179</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303113106</t>
+          <t>https://m.place.naver.com/place/1328657179</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5236,39 +5212,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>오브네일</t>
+          <t>달처럼예뻐라</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ofrang@naver.com</t>
+          <t>haru_04@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1370-9776</t>
+          <t>0507-1494-2578</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로366번길 19 . 1층</t>
+          <t>부산광역시 사상구 운산로 28 상가13동 2층 205호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gxixiTG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5284,22 +5260,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R52" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5308,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1071928305</t>
+          <t>1699052156</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071928305</t>
+          <t>https://m.place.naver.com/place/1699052156</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5330,24 +5306,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일존 이마트사상점</t>
+          <t>쏭네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>marilov21@naver.com</t>
+          <t>ssongnail01@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>051-710-6535</t>
+          <t>0507-1355-9745</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 17 이마트 사상점 1층</t>
+          <t>부산광역시 사상구 양지로24번길 2 1층 쏭네일</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5387,14 +5363,14 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
         <v>2</v>
       </c>
-      <c r="R53" t="n">
-        <v>17</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5402,17 +5378,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>31229660</t>
+          <t>1669157044</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229660</t>
+          <t>https://m.place.naver.com/place/1669157044</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5424,25 +5400,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
+          <t>네일이지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nanamoon23@naver.com</t>
+          <t>rlathdms96@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1390-3978</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 91 3층</t>
+          <t>부산광역시 사상구 엄궁로179번가길 17-9 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jbeauty_nailsalon?igsh=NG5ubXc0MjdocWMx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_2ji</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5477,13 +5457,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5492,17 +5472,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2006084959</t>
+          <t>2022406101</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006084959</t>
+          <t>https://m.place.naver.com/place/2022406101</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5514,29 +5494,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>예블링네일</t>
+          <t>아마폴라뷰티</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>thsghkwlsas@naver.com</t>
+          <t>amapola3221016@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1462-0158</t>
+          <t>0507-1325-2164</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 덕상로 19-1 1층 예블링네일</t>
+          <t>부산광역시 사상구 대동로 133-2 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yebling_nail</t>
+          <t>https://www.instagram.com/amapola_official_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5571,13 +5551,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="R55" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5586,17 +5566,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1115413707</t>
+          <t>1049170292</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115413707</t>
+          <t>https://m.place.naver.com/place/1049170292</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5608,25 +5588,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>지혜네일샵</t>
+          <t>네일파크</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>liz_kang@naver.com</t>
+          <t>eunmijan@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1441-4147</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 삼덕로46번안길 28 조선사</t>
+          <t>부산광역시 사상구 가야대로360번길 1 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nailpark</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5636,7 +5620,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5657,17 +5641,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,17 +5660,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1658577122</t>
+          <t>1218794769</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1658577122</t>
+          <t>https://m.place.naver.com/place/1218794769</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5698,25 +5682,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>홍네일</t>
+          <t>네일썸</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6569807@naver.com</t>
+          <t>un6ee@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1323-7075</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로309번길 49</t>
+          <t>부산광역시 사상구 사상로212번길 38 2층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.some_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5726,7 +5714,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5747,17 +5735,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5754,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1603273526</t>
+          <t>2052010949</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1603273526</t>
+          <t>https://m.place.naver.com/place/2052010949</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5788,39 +5776,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>뚜디살롱</t>
+          <t>이쁘네.일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>lliii99966@naver.com</t>
+          <t>haennyo7997@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1468-8936</t>
+          <t>0507-1438-2541</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로284번길 2 럭키종합상가 18동 1층 8호</t>
+          <t>부산광역시 사상구 가야대로 295 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ddudi_salon</t>
+          <t>http://이쁘네일.kr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5845,13 +5833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>319</v>
+        <v>150</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="R58" t="n">
-        <v>330</v>
+        <v>203</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5848,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1682930248</t>
+          <t>1106172366</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682930248</t>
+          <t>https://m.place.naver.com/place/1106172366</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5882,34 +5870,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>모라네일</t>
+          <t>제제네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jessicanail@naver.com</t>
+          <t>qnfnqnqn13@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1379-0989</t>
+          <t>0507-1412-8079</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로51번길 16 1층(모라네일)/구 헤이진 네일</t>
+          <t>부산광역시 사상구 사상로292번길 28 1층 JEJENAIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/heyjin2019</t>
+          <t>https://pf.kakao.com/_KxbBEn</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5930,7 +5918,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5939,13 +5927,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R59" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5942,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1537116650</t>
+          <t>1926033569</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537116650</t>
+          <t>https://m.place.naver.com/place/1926033569</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5976,34 +5964,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>포인트뷰티</t>
+          <t>라비앙로즈네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>handlife@naver.com</t>
+          <t>ogamza_@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1344-0097</t>
+          <t>0507-1340-8327</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 양지로30번길 9 상가 2층</t>
+          <t>부산광역시 사상구 가야대로 288 창조센츄리 상가 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_point_beauty</t>
+          <t>https://pf.kakao.com/_CZBEs</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6024,7 +6012,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6033,13 +6021,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +6036,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1699053374</t>
+          <t>1335031344</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699053374</t>
+          <t>https://m.place.naver.com/place/1335031344</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6070,39 +6058,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>슈가네일</t>
+          <t>네일와요</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sugar_nail@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>051-316-4145</t>
+          <t>0507-1364-2465</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 288</t>
+          <t>부산광역시 사상구 사상로223번길 23 서희센트럴스타힐스 106동 2층 204호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_NQdnG</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6118,22 +6106,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6142,17 +6130,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1626070548</t>
+          <t>1509491646</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626070548</t>
+          <t>https://m.place.naver.com/place/1509491646</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6164,29 +6152,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>예쁜손톱방</t>
+          <t>유유네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hina_lanayahgas@naver.com</t>
+          <t>thgus4613@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1337-2616</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로 109-14 상가동 1층 101호</t>
+          <t>부산광역시 사상구 가야대로306번길 79</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeun_nail_bang</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6196,7 +6180,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6217,17 +6201,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6236,17 +6220,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1237764066</t>
+          <t>37979962</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237764066</t>
+          <t>https://m.place.naver.com/place/37979962</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6258,24 +6242,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>비쥬네일</t>
+          <t>퀸즈네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h2425@naver.com</t>
+          <t>qu_eenz@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1447-8896</t>
+          <t>051-322-1145</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 새벽로 173</t>
+          <t>부산광역시 사상구 괘감로 97</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6315,13 +6299,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6330,17 +6314,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1956450361</t>
+          <t>21505702</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956450361</t>
+          <t>https://m.place.naver.com/place/21505702</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6352,29 +6336,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일하랑</t>
+          <t>일루아네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>harang9488@naver.com</t>
+          <t>chltnwl900@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1466-1336</t>
+          <t>0507-1497-8287</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 54 포르투나더테라스 2층 210호</t>
+          <t>부산광역시 사상구 엄궁북로 40 롯데캐슬상가 1동 104호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__ha_rang</t>
+          <t>http://www.instagram.com/illua_suji</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6400,7 +6384,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6409,13 +6393,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6424,17 +6408,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1454851530</t>
+          <t>613016122</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454851530</t>
+          <t>https://m.place.naver.com/place/613016122</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6446,29 +6430,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>네로뷰티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>nr08@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1303-2195</t>
+          <t>0507-1316-7440</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도보라타운252호</t>
+          <t>부산광역시 사상구 백양대로 974 2층 네로뷰티(진갈비 2층)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/shy5VQef</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6478,7 +6462,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6494,22 +6478,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R65" t="n">
-        <v>22</v>
+        <v>315</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6518,17 +6502,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1549283623</t>
+          <t>1785862913</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549283623</t>
+          <t>https://m.place.naver.com/place/1785862913</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6540,29 +6524,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>일루아네일</t>
+          <t>루미아 네일 뷰티케어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>chltnwl900@naver.com</t>
+          <t>pochun_ant@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1497-8287</t>
+          <t>0507-1345-8988</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁북로 40 롯데캐슬상가 1동 104호</t>
+          <t>부산광역시 사상구 백양대로907번가길 54 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/illua_suji</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6572,7 +6556,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6593,17 +6577,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6612,17 +6596,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>613016122</t>
+          <t>2095013714</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/613016122</t>
+          <t>https://m.place.naver.com/place/2095013714</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6634,29 +6618,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>아이리스네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>kitty666@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>051-315-1007</t>
+          <t>051-319-5413</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 774-1</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1413호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_grimi</t>
+          <t>https://blog.naver.com/kitty666</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6671,7 +6655,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6687,17 +6671,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6706,17 +6690,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1051850286</t>
+          <t>35228104</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051850286</t>
+          <t>https://m.place.naver.com/place/35228104</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6728,34 +6712,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23도네일</t>
+          <t>네일송송 사상점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>dbcom36@naver.com</t>
+          <t>ssons_shop@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1339-5124</t>
+          <t>051-303-7333</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로233번길 16 1층 101호</t>
+          <t>부산광역시 사상구 백양대로 712 남영아파트상가 2동 1층 8호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WaGxjxb</t>
+          <t>https://blog.naver.com/ssons_shop</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6765,7 +6749,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6776,22 +6760,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>216</v>
+        <v>325</v>
       </c>
       <c r="Q68" t="n">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="R68" t="n">
-        <v>271</v>
+        <v>501</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6800,17 +6784,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1908955863</t>
+          <t>1824794292</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1908955863</t>
+          <t>https://m.place.naver.com/place/1824794292</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6806,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>유유네일</t>
+          <t>네일블라썸</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>thgus4613@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6835,7 +6819,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로306번길 79</t>
+          <t>부산광역시 사상구 대동로 94 반도상가 2층 238호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6875,13 +6859,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,17 +6874,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37979962</t>
+          <t>2027108055</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37979962</t>
+          <t>https://m.place.naver.com/place/2027108055</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6912,29 +6896,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>가꾸다네일</t>
+          <t>핸드네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>chl4550@naver.com</t>
+          <t>jessicanail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1439-1785</t>
+          <t>0507-1379-4125</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 208-1 12층 1202호</t>
+          <t>부산광역시 사상구 백양대로 916 우성아파트 상가1동 111호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gakkuda_nail1</t>
+          <t>https://blog.naver.com/jessicanail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6949,7 +6933,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6969,13 +6953,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,17 +6968,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2009578695</t>
+          <t>32794875</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009578695</t>
+          <t>https://m.place.naver.com/place/32794875</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7006,24 +6990,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일톡톡</t>
+          <t>비쥬네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nailtoctoc@naver.com</t>
+          <t>h2425@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1333-0960</t>
+          <t>0507-1447-8896</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로1210번길 78 1층</t>
+          <t>부산광역시 사상구 새벽로 173</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7063,13 +7047,13 @@
         </is>
       </c>
       <c r="P71" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7078,17 +7062,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1484262326</t>
+          <t>1956450361</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484262326</t>
+          <t>https://m.place.naver.com/place/1956450361</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7100,39 +7084,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>케이뷰티</t>
+          <t>네일혜현</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bi1142@naver.com</t>
+          <t>hyeon_2124@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>051-669-6355</t>
+          <t>0507-1306-1292</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 910</t>
+          <t>부산광역시 사상구 광장로97번길 46 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhxiPKK/chat</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7148,22 +7132,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7172,17 +7156,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1104145262</t>
+          <t>1925352608</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1104145262</t>
+          <t>https://m.place.naver.com/place/1925352608</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7194,29 +7178,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>숲,Nail Studio</t>
+          <t>오라네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>y_unjiv_v@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1389-2939</t>
+          <t>0507-1361-8337</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로88번길 17 1층</t>
+          <t>부산광역시 사상구 낙동대로1210번길 88</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soopnail_</t>
+          <t>http://www.instagram.com/_O_ranail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7251,13 +7235,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,17 +7250,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1882913328</t>
+          <t>1910001099</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882913328</t>
+          <t>https://m.place.naver.com/place/1910001099</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7288,29 +7272,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>핸드네일</t>
+          <t>포인트뷰티</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jessicanail@naver.com</t>
+          <t>vjvmf_love@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1379-4125</t>
+          <t>0507-1344-0097</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 916 우성아파트 상가1동 111호</t>
+          <t>부산광역시 사상구 양지로30번길 9 상가 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jessicanail</t>
+          <t>https://www.instagram.com/_point_beauty</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7325,7 +7309,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7345,13 +7329,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>345</v>
+        <v>29</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>369</v>
+        <v>33</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,17 +7344,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>32794875</t>
+          <t>1699053374</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32794875</t>
+          <t>https://m.place.naver.com/place/1699053374</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7382,29 +7366,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>하얀네일</t>
+          <t>가꾸다네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>whitenail27@naver.com</t>
+          <t>chl4550@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1490-1110</t>
+          <t>0507-1439-1785</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 동주로 24 1층 하얀네일</t>
+          <t>부산광역시 사상구 사상로 208-1 12층 1202호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/hayan_nail</t>
+          <t>https://www.instagram.com/gakkuda_nail1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7439,13 +7423,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,17 +7438,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1581947459</t>
+          <t>2009578695</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581947459</t>
+          <t>https://m.place.naver.com/place/2009578695</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7476,29 +7460,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>클라라네일</t>
+          <t>네일하는언니</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>laura1016@naver.com</t>
+          <t>cmk11273@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1352-5400</t>
+          <t>051-987-7998</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1401호</t>
+          <t>부산광역시 사상구 사상로342번길 37 블루밍@상가동1층103호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailunnie_ja</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7508,7 +7492,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7524,22 +7508,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,17 +7532,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>37638497</t>
+          <t>1400451423</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37638497</t>
+          <t>https://m.place.naver.com/place/1400451423</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7570,29 +7554,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>라니뷰티</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>amore_rani@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1382-0261</t>
+          <t>0507-1303-2195</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 998-1 2층</t>
+          <t>부산광역시 사상구 대동로 94 반도보라타운252호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://instagram.com/_r._an._i._</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7602,7 +7586,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7623,17 +7607,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R77" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7642,17 +7626,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1178399753</t>
+          <t>1549283623</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178399753</t>
+          <t>https://m.place.naver.com/place/1549283623</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7664,29 +7648,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>퀸네일</t>
+          <t>손블링네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>miinijk@naver.com</t>
+          <t>riplim@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1380-2805</t>
+          <t>0507-1377-2398</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자 1층 110호 퀸네일</t>
+          <t>부산광역시 사상구 가야대로306번길 79 1층 손블링네일</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sonbling_nail/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7696,7 +7680,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7717,17 +7701,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R78" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7736,17 +7720,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1679312982</t>
+          <t>2007060512</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679312982</t>
+          <t>https://m.place.naver.com/place/2007060512</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7758,24 +7742,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>백아네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>love_dlehdgo@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1392-7397</t>
+          <t>0507-1338-8558</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 884 상가동 1층 121호</t>
+          <t>부산광역시 사상구 대동로 94 상가동 243호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7815,13 +7799,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7830,17 +7814,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1354678970</t>
+          <t>1180139663</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354678970</t>
+          <t>https://m.place.naver.com/place/1180139663</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7852,25 +7836,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>맑은네일</t>
+          <t>네일도로시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>rhd0209@naver.com</t>
+          <t>whektha1613@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1316-9113</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 106 목화아파트상가 3층 310호</t>
+          <t>부산광역시 사상구 엄궁로203번길 38 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://instagram.com/malgeunnail</t>
+          <t>https://instagram.com/_nail_dorothy_?igshid=irihcx1mq6ow</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7905,13 +7893,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7920,17 +7908,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1433389520</t>
+          <t>1033126412</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433389520</t>
+          <t>https://m.place.naver.com/place/1033126412</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7942,25 +7930,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>주네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>jinrose22@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1309-0526</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자상가 2층 273호</t>
+          <t>부산광역시 사상구 엄궁로179번길 21 3층 주네일</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/joonail623</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7970,7 +7962,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7991,17 +7983,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8010,17 +8002,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>31505917</t>
+          <t>1588835862</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31505917</t>
+          <t>https://m.place.naver.com/place/1588835862</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8024,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>hackerstalk11@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8045,12 +8037,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도상가 2층 238호</t>
+          <t>부산광역시 사상구 엄궁북로 59 롯데캐슬리버 401동앞 상가1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/thumb__nail__?igshid=16cyosojl8iua</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8060,7 +8052,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8081,17 +8073,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8100,17 +8092,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2027108055</t>
+          <t>1022811581</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027108055</t>
+          <t>https://m.place.naver.com/place/1022811581</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8122,29 +8114,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일하는언니</t>
+          <t>네일포레</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>cmk11273@naver.com</t>
+          <t>nail_foret@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>051-987-7998</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로342번길 37 블루밍@상가동1층103호</t>
+          <t>부산광역시 사상구 사상로90번길 6 1층 왼쪽</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunnie_ja</t>
+          <t>https://www.instagram.com/nail_for.et?igsh=Zjk2cnE5emQ4MDR1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8170,7 +8158,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8179,13 +8167,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8194,17 +8182,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1400451423</t>
+          <t>2032419101</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400451423</t>
+          <t>https://m.place.naver.com/place/2032419101</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8216,29 +8204,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>빛날희네일</t>
+          <t>예쁜손톱방</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>kimmihee4@naver.com</t>
+          <t>hina_lanayahgas@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1358-0304</t>
+          <t>0507-1337-2616</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로104번길 27</t>
+          <t>부산광역시 사상구 학감대로 109-14 상가동 1층 101호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail03</t>
+          <t>http://www.instagram.com/yebbeun_nail_bang</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8273,13 +8261,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q84" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8288,17 +8276,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1358743723</t>
+          <t>1237764066</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358743723</t>
+          <t>https://m.place.naver.com/place/1237764066</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8310,39 +8298,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>이쁘네.일</t>
+          <t>너도,네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>haennyo7997@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1438-2541</t>
+          <t>0507-1399-2081</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 295 1층</t>
+          <t>부산광역시 사상구 주례로9번길 83 1층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://이쁘네일.kr</t>
+          <t>http://www.instagram.com/nido_nail</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8367,13 +8355,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="Q85" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8382,17 +8370,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1106172366</t>
+          <t>1917089461</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106172366</t>
+          <t>https://m.place.naver.com/place/1917089461</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8404,29 +8392,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>초록뷰티</t>
+          <t>맑은네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8852561@naver.com</t>
+          <t>rhd0209@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1496-1644</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 883 상가 10동 2층 206호</t>
+          <t>부산광역시 사상구 대동로 106 목화아파트상가 3층 310호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chorok__beauty?igsh=Zm1vNDRnNHRueXJ6&amp;utm_source=qr</t>
+          <t>http://instagram.com/malgeunnail</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8461,10 +8445,10 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="R86" t="n">
         <v>24</v>
@@ -8476,17 +8460,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1679896666</t>
+          <t>1433389520</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679896666</t>
+          <t>https://m.place.naver.com/place/1433389520</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8498,25 +8482,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>샛별네일아트</t>
+          <t>라니뷰티</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>amore_rani@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1382-0261</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 2동 236호 (학장동,반도프라자)</t>
+          <t>부산광역시 사상구 백양대로 998-1 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_r._an._i._</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8526,7 +8514,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8547,17 +8535,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8566,17 +8554,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1396422090</t>
+          <t>1178399753</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396422090</t>
+          <t>https://m.place.naver.com/place/1178399753</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8658,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8682,29 +8670,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>손블링네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>to_nail@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1377-2398</t>
+          <t>051-315-1007</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로306번길 79 1층 손블링네일</t>
+          <t>부산광역시 사상구 낙동대로 774-1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sonbling_nail/</t>
+          <t>http://instagram.com/nail_grimi</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8739,13 +8727,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8754,17 +8742,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2007060512</t>
+          <t>1051850286</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007060512</t>
+          <t>https://m.place.naver.com/place/1051850286</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8776,29 +8764,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일썸</t>
+          <t>로코네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rlarldms7531@naver.com</t>
+          <t>u_love118@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1323-7075</t>
+          <t>0507-1391-7108</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로212번길 38 2층</t>
+          <t>부산광역시 사상구 사상로238번길 5 . 1층 루니움뷰티&amp;케어</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.some_</t>
+          <t>https://www.instagram.com/_loconail</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8824,7 +8812,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8833,13 +8821,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>33</v>
+        <v>257</v>
       </c>
       <c r="Q90" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="R90" t="n">
-        <v>40</v>
+        <v>274</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8848,17 +8836,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2052010949</t>
+          <t>1303113106</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052010949</t>
+          <t>https://m.place.naver.com/place/1303113106</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8870,29 +8858,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>네일하랑</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>harang9488@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1331-6537</t>
+          <t>0507-1466-1336</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 372-16 상가3층 제이제이네일</t>
+          <t>부산광역시 사상구 광장로 54 포르투나더테라스 2층 210호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>http://instagram.com/j.j__nail</t>
+          <t>https://www.instagram.com/nail__ha_rang</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8918,7 +8906,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8927,13 +8915,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="Q91" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="R91" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8942,17 +8930,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1221988261</t>
+          <t>1454851530</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221988261</t>
+          <t>https://m.place.naver.com/place/1454851530</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8964,29 +8952,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>네일하이디</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>smwls0114@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1399-0460</t>
+          <t>0507-1341-4976</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 상가동 2층 282호</t>
+          <t>부산광역시 사상구 백양대로504번길 2 1층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_hi.d</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8996,7 +8984,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9017,17 +9005,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9036,17 +9024,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1060258369</t>
+          <t>1061733115</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060258369</t>
+          <t>https://m.place.naver.com/place/1061733115</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9058,29 +9046,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>주강희 네일샵</t>
+          <t>네일더드림</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>overflow0409@naver.com</t>
+          <t>rabbit0577@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>070-4413-4141</t>
+          <t>051-323-0807</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 884 우신모라아파트</t>
+          <t>부산광역시 사상구 엄궁로 195</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_thedream/</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9090,7 +9078,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9111,17 +9099,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9130,17 +9118,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1354914865</t>
+          <t>517958118</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354914865</t>
+          <t>https://m.place.naver.com/place/517958118</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9152,34 +9140,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>네일혜현</t>
+          <t>하이네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>hyeon_2124@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1306-1292</t>
+          <t>0507-1308-0940</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로97번길 46 1층</t>
+          <t>부산광역시 사상구 사상로342번길 21 벽산늘푸른상가 2층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhxiPKK/chat</t>
+          <t>http://www.instagram.com/hi_nailll</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9200,7 +9188,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9209,13 +9197,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9224,17 +9212,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1925352608</t>
+          <t>1223881417</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925352608</t>
+          <t>https://m.place.naver.com/place/1223881417</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9246,25 +9234,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>요술손</t>
+          <t>네일마루&amp;카페</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>yosulson_party@naver.com</t>
+          <t>suji6777@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1321-4724</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로250번길 22</t>
+          <t>부산광역시 사상구 백양대로 372-22 반도보라메머드타운상가 209호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailmaru</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9274,7 +9266,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9295,14 +9287,14 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
         <v>10</v>
@@ -9314,17 +9306,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1330709122</t>
+          <t>1730313997</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330709122</t>
+          <t>https://m.place.naver.com/place/1730313997</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9336,29 +9328,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>오라네일</t>
+          <t>씨네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>wjsska1907@naver.com</t>
+          <t>ansh1128@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1361-8337</t>
+          <t>0507-1382-8160</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로1210번길 88</t>
+          <t>부산광역시 사상구 낙동대로 733 롯데마트 사상점 3층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_O_ranail</t>
+          <t>http://www.instagram.com/cnail_3</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9393,13 +9385,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9408,17 +9400,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1910001099</t>
+          <t>16801995</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910001099</t>
+          <t>https://m.place.naver.com/place/16801995</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9430,34 +9422,34 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>제제네일</t>
+          <t>옐블링</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>qnfnqnqn13@naver.com</t>
+          <t>kkonge_@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1412-8079</t>
+          <t>0507-1347-4690</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로292번길 28 1층 JEJENAIL</t>
+          <t>부산광역시 사상구 사상로238번길 35 1층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_KxbBEn</t>
+          <t>https://www.instagram.com/yelbling___</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9487,13 +9479,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="Q97" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9502,17 +9494,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1926033569</t>
+          <t>1434085437</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926033569</t>
+          <t>https://m.place.naver.com/place/1434085437</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9524,34 +9516,34 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네로뷰티</t>
+          <t>이상한나라뷰티</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>nr08@naver.com</t>
+          <t>ria2101@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1316-7440</t>
+          <t>0507-1373-2406</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 974 2층 네로뷰티(진갈비 2층)</t>
+          <t>부산광역시 사상구 광장로37번길 84 1층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/shy5VQef</t>
+          <t>http://pf.kakao.com/_tauxcG</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9581,13 +9573,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="Q98" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>313</v>
+        <v>19</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9596,17 +9588,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1785862913</t>
+          <t>1451827533</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785862913</t>
+          <t>https://m.place.naver.com/place/1451827533</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9618,29 +9610,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>옐블링</t>
+          <t>HERO 네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kkonge_@naver.com</t>
+          <t>hero_0304@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1347-4690</t>
+          <t>0507-1368-2076</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 35 1층</t>
+          <t>부산광역시 사상구 백양대로 760 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yelbling___</t>
+          <t>https://www.instagram.com/hero_nail_1101</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9666,7 +9658,7 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -9675,13 +9667,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9690,17 +9682,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1434085437</t>
+          <t>1884120549</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434085437</t>
+          <t>https://m.place.naver.com/place/1884120549</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9712,29 +9704,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>백아네일</t>
+          <t>단미뷰티</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>love_dlehdgo@naver.com</t>
+          <t>kmlove123@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1338-8558</t>
+          <t>0507-1390-0815</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 상가동 243호</t>
+          <t>부산광역시 사상구 모라로110번길 5 2층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/danmi__bt/</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9744,7 +9736,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9765,17 +9757,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9784,17 +9776,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1180139663</t>
+          <t>1759913260</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180139663</t>
+          <t>https://m.place.naver.com/place/1759913260</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9806,39 +9798,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>네일와요</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1364-2465</t>
+          <t>0507-1392-7397</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로223번길 23 서희센트럴스타힐스 106동 2층 204호</t>
+          <t>부산광역시 사상구 백양대로 884 상가동 1층 121호</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NQdnG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9854,22 +9846,22 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9878,17 +9870,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1509491646</t>
+          <t>1354678970</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509491646</t>
+          <t>https://m.place.naver.com/place/1354678970</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9892,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>레푸스 사상점</t>
+          <t>무이네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mimongmnn@naver.com</t>
+          <t>baeyou0417@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -9913,17 +9905,17 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 208-1 10층</t>
+          <t>부산광역시 사상구 운산로 21 1층 (부산광역시 사상구 삼락동 418-8 1층)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://litt.ly/refuss_nail4season_busan</t>
+          <t>https://www.instagram.com/mooinail_uz</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9953,13 +9945,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>660</v>
+        <v>92</v>
       </c>
       <c r="Q102" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>820</v>
+        <v>93</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9968,17 +9960,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1044773647</t>
+          <t>1347978558</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044773647</t>
+          <t>https://m.place.naver.com/place/1347978558</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9990,29 +9982,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>아마폴라뷰티</t>
+          <t>네일k</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>amapola3221016@naver.com</t>
+          <t>oio7845@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1325-2164</t>
+          <t>0507-1313-2205</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 133-2 2층</t>
+          <t>부산광역시 사상구 백양대로 490 주례1차동일아파트 106동 1층 107-2호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/amapola_official_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10022,7 +10014,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10043,17 +10035,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="Q103" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10062,17 +10054,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1049170292</t>
+          <t>1029204849</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049170292</t>
+          <t>https://m.place.naver.com/place/1029204849</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10084,39 +10076,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이상한나라뷰티</t>
+          <t>TOAS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ria2101@naver.com</t>
+          <t>shintc@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1373-2406</t>
+          <t>051-325-9903</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로37번길 84 1층</t>
+          <t>부산광역시 사상구 운산로 22</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tauxcG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10132,22 +10124,22 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10156,17 +10148,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1451827533</t>
+          <t>1997973035</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451827533</t>
+          <t>https://m.place.naver.com/place/1997973035</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10178,29 +10170,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>네일콩</t>
+          <t>슈가네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>besmlsk@naver.com</t>
+          <t>junge1004j@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1306-3190</t>
+          <t>051-316-4145</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 덕상로 10 오양상가 303호 네일콩</t>
+          <t>부산광역시 사상구 가야대로 288</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailkong.k</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10210,7 +10202,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10231,18 +10223,18 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
         <v>2</v>
       </c>
-      <c r="R105" t="n">
-        <v>13</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>X</t>
@@ -10250,17 +10242,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1444223522</t>
+          <t>1626070548</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444223522</t>
+          <t>https://m.place.naver.com/place/1626070548</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10272,30 +10264,34 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>눈부시네.일</t>
+          <t>손톱공주</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>dole222@naver.com</t>
+          <t>ha___60@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>051-321-0453</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로9번길 3 눈부시네.일</t>
+          <t>부산광역시 사상구 대동로 98</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://toss-order.tossplace.com/booking/N2L40xfR9x2ivsY</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10321,18 +10317,18 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
         <v>1</v>
       </c>
-      <c r="R106" t="n">
-        <v>31</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>X</t>
@@ -10340,17 +10336,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2145722253</t>
+          <t>38412266</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2145722253</t>
+          <t>https://m.place.naver.com/place/38412266</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10362,29 +10358,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>주네일</t>
+          <t>야시 속눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jinrose22@naver.com</t>
+          <t>nice0304011@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1406-7510</t>
+          <t>0507-1303-4262</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 28 1층 주네일</t>
+          <t>부산광역시 사상구 사상로 484 1층 야시속눈썹</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/7junail7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10394,7 +10390,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10415,17 +10411,17 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q107" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10434,17 +10430,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1705139517</t>
+          <t>1656610719</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1705139517</t>
+          <t>https://m.place.naver.com/place/1656610719</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10456,29 +10452,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>너도,네일</t>
+          <t>주강희 네일샵</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>overflow0409@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1399-2081</t>
+          <t>070-4413-4141</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로9번길 83 1층</t>
+          <t>부산광역시 사상구 백양대로 884 우신모라아파트</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nido_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10488,7 +10484,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10509,17 +10505,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10528,17 +10524,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1917089461</t>
+          <t>1354914865</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917089461</t>
+          <t>https://m.place.naver.com/place/1354914865</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10550,39 +10546,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>용이뷰티</t>
+          <t>23도네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>yurim012@naver.com</t>
+          <t>dbcom36@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1406-6990</t>
+          <t>0507-1339-5124</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 950</t>
+          <t>부산광역시 사상구 사상로233번길 16 1층 101호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_WaGxjxb</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10598,7 +10594,7 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -10607,13 +10603,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>6</v>
+        <v>216</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R109" t="n">
-        <v>6</v>
+        <v>271</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10622,17 +10618,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>38521099</t>
+          <t>1908955863</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38521099</t>
+          <t>https://m.place.naver.com/place/1908955863</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10644,29 +10640,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>수아한네일</t>
+          <t>뚜디살롱</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ksh_6563@naver.com</t>
+          <t>lliii99966@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1441-0277</t>
+          <t>0507-1468-8936</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 2층 248호</t>
+          <t>부산광역시 사상구 가야대로284번길 2 럭키종합상가 18동 1층 8호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/suahan_nail?igsh=MTZnYnRmNmFnNTQ4MA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/ddudi_salon</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10701,13 +10697,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="Q110" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R110" t="n">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10716,17 +10712,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1798118492</t>
+          <t>1682930248</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798118492</t>
+          <t>https://m.place.naver.com/place/1682930248</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10738,39 +10734,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>썬네일</t>
+          <t>네일존 이마트사상점</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>sunnail3024@naver.com</t>
+          <t>marilov21@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1356-6980</t>
+          <t>051-710-6535</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 1층 1번가 1337,1338호(괘법동, 르네시떼)</t>
+          <t>부산광역시 사상구 광장로 17 이마트 사상점 1층</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000016770</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10791,17 +10787,17 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10810,17 +10806,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1046901734</t>
+          <t>31229660</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046901734</t>
+          <t>https://m.place.naver.com/place/31229660</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10832,34 +10828,30 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>핑크네일</t>
+          <t>레푸스 사상점</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>go8282c@naver.com</t>
+          <t>mimongmnn@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0507-1334-0020</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로 15 3층 핑크네일</t>
+          <t>부산광역시 사상구 사상로 208-1 10층</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pinknail_busan</t>
+          <t>https://litt.ly/refuss_nail4season_busan</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10889,13 +10881,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>15</v>
+        <v>663</v>
       </c>
       <c r="Q112" t="n">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="R112" t="n">
-        <v>347</v>
+        <v>823</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10904,17 +10896,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>36924982</t>
+          <t>1044773647</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36924982</t>
+          <t>https://m.place.naver.com/place/1044773647</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10926,29 +10918,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>네일송송 사상점</t>
+          <t>숲,Nail Studio</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ssons_shop@naver.com</t>
+          <t>y_unjiv_v@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>051-303-7333</t>
+          <t>0507-1389-2939</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 712 남영아파트상가 2동 1층 8호</t>
+          <t>부산광역시 사상구 모라로88번길 17 1층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssons_shop</t>
+          <t>https://www.instagram.com/soopnail_</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10963,7 +10955,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10983,13 +10975,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10998,17 +10990,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1824794292</t>
+          <t>1882913328</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824794292</t>
+          <t>https://m.place.naver.com/place/1882913328</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11020,25 +11012,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>미유네일</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>wnsdudgpqls@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1331-6537</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로233번길 14 1층 102호</t>
+          <t>부산광역시 사상구 백양대로 372-16 상가3층 제이제이네일</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/stxAgifc</t>
+          <t>http://instagram.com/j.j__nail</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11064,7 +11060,7 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -11073,13 +11069,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11088,17 +11084,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>2007447861</t>
+          <t>1221988261</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007447861</t>
+          <t>https://m.place.naver.com/place/1221988261</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11110,29 +11106,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>손톱공주</t>
+          <t>네일더끌림</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ha___60@naver.com</t>
+          <t>rktngpfud@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>051-321-0453</t>
+          <t>051-977-0977</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 98</t>
+          <t>부산광역시 사상구 운산로 47 네일더끌림</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rktngpfud</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11142,12 +11138,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11163,17 +11159,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R115" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11182,56 +11178,56 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>38412266</t>
+          <t>1805551094</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38412266</t>
+          <t>https://m.place.naver.com/place/1805551094</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>살롱 메이브</t>
+          <t>늘예쁨 네일</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>salon_maeve@naver.com</t>
+          <t>pig_malion_@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1419-2145</t>
+          <t>0507-1356-6612</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로255번길 5 롯데캐슬골드스마트상가 115동 103호</t>
+          <t>부산광역시 사상구 가야대로 369 1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/salon_maeve</t>
+          <t>http://pf.kakao.com/_xlQmxnn</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11241,7 +11237,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11252,41 +11248,135 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>456</v>
+        <v>90</v>
       </c>
       <c r="Q116" t="n">
+        <v>7</v>
+      </c>
+      <c r="R116" t="n">
+        <v>97</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2079016042</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079016042</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>살롱 메이브</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>salon_maeve@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0507-1419-2145</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>부산광역시 사상구 가야대로255번길 5 롯데캐슬골드스마트상가 115동 103호</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/salon_maeve</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>463</v>
+      </c>
+      <c r="Q117" t="n">
         <v>21</v>
       </c>
-      <c r="R116" t="n">
-        <v>477</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
+      <c r="R117" t="n">
+        <v>484</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
         <is>
           <t>1093803171</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="U117" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1093803171</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/사상구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/사상구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>썬뷰티네일샵</t>
+          <t>달처럼예뻐라</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>artst_snu@naver.com</t>
+          <t>haru_04@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1375-2696</t>
+          <t>0507-1494-2578</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로342번길 21 206호</t>
+          <t>부산광역시 사상구 운산로 28 상가13동 2층 205호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunnailshop2696</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1498701306</t>
+          <t>1699052156</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498701306</t>
+          <t>https://m.place.naver.com/place/1699052156</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>꿈꾸는네일</t>
+          <t>네일하는언니</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dreamnail@naver.com</t>
+          <t>cmk11273@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>051-987-7998</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번길 9-8 꿈꾸는네일</t>
+          <t>부산광역시 사상구 사상로342번길 37 블루밍@상가동1층103호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_dream.nail</t>
+          <t>https://www.instagram.com/nailunnie_ja</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -702,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -714,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1792266910</t>
+          <t>1400451423</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792266910</t>
+          <t>https://m.place.naver.com/place/1400451423</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -748,20 +752,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>슈가네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>junge1004j@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>051-316-4145</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자상가 2층 273호</t>
+          <t>부산광역시 사상구 가야대로 288</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31505917</t>
+          <t>1626070548</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31505917</t>
+          <t>https://m.place.naver.com/place/1626070548</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -838,24 +846,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마녀손톱</t>
+          <t>퀸네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>vitaminiya@naver.com</t>
+          <t>queen9845@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>051-311-2204</t>
+          <t>0507-1380-2805</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로494번길 19</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자 1층 110호 퀸네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -895,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1020368554</t>
+          <t>1679312982</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1020368554</t>
+          <t>https://m.place.naver.com/place/1679312982</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -932,29 +940,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일애 푸스케어 부산엄궁점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>fusscare_nailaee@naver.com</t>
-        </is>
-      </c>
+          <t>제이뷰티</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1379-0163</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 144 1층 105호</t>
+          <t>부산광역시 사상구 광장로 91 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.aee</t>
+          <t>https://www.instagram.com/jbeauty_nailsalon?igsh=NG5ubXc0MjdocWMx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>156</v>
+        <v>3</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1438869369</t>
+          <t>2006084959</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438869369</t>
+          <t>https://m.place.naver.com/place/2006084959</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1026,34 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>썬네일</t>
+          <t>아이리스네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sunnail3024@naver.com</t>
+          <t>kitty666@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1356-6980</t>
+          <t>051-319-5413</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 1층 1번가 1337,1338호(괘법동, 르네시떼)</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1413호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000016770</t>
+          <t>https://blog.naver.com/kitty666</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1046901734</t>
+          <t>35228104</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046901734</t>
+          <t>https://m.place.naver.com/place/35228104</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1120,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쏭네일</t>
+          <t>네일존 이마트사상점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ssongnail01@naver.com</t>
+          <t>ekgus618@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1372-6483</t>
+          <t>051-710-6535</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로776번길 36 1층</t>
+          <t>부산광역시 사상구 광장로 17 이마트 사상점 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1484173928</t>
+          <t>31229660</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484173928</t>
+          <t>https://m.place.naver.com/place/31229660</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일제이</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>jiwon3716@naver.com</t>
-        </is>
-      </c>
+          <t>네리나네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1308-3976</t>
+          <t>0507-1428-1560</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 326 1층 네일제이</t>
+          <t>부산광역시 사상구 강선로 18 1층 네리나 네일&amp;뷰티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiwon3716</t>
+          <t>https://www.instagram.com/nerina_nail?igsh=MXhiZ296NXdneXcw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1247,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1282,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1944314268</t>
+          <t>1273947079</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944314268</t>
+          <t>https://m.place.naver.com/place/1273947079</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1304,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>케이뷰티</t>
+          <t>네일하루 사상본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bi1142@naver.com</t>
+          <t>raooonnn@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-669-6355</t>
+          <t>0507-1311-3336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 910</t>
+          <t>부산광역시 사상구 사상로 214 3층 네일하루</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailharu3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1336,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1361,17 +1357,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1104145262</t>
+          <t>1328657179</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1104145262</t>
+          <t>https://m.place.naver.com/place/1328657179</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1402,25 +1398,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모라네일</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jessicanail@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1331-6537</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로51번길 16</t>
+          <t>부산광역시 사상구 백양대로 372-16 상가3층 제이제이네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/j.j__nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2143022752</t>
+          <t>1221988261</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2143022752</t>
+          <t>https://m.place.naver.com/place/1221988261</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1492,25 +1492,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>지혜네일샵</t>
+          <t>HERO 네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>liz_kang@naver.com</t>
+          <t>hero_0304@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1368-2076</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 삼덕로46번안길 28 조선사</t>
+          <t>부산광역시 사상구 백양대로 760 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hero_nail_1101</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1520,7 +1524,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1541,17 +1545,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1560,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1658577122</t>
+          <t>1884120549</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1658577122</t>
+          <t>https://m.place.naver.com/place/1884120549</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1582,29 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일로움 &amp; 속눈썹</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vjkzmf10@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1370-0917</t>
+          <t>051-315-1007</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 36 한신아파트1차 상가 2층 네일로움</t>
+          <t>부산광역시 사상구 낙동대로 774-1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailroum_</t>
+          <t>http://instagram.com/nail_grimi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1639,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>301</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>546</v>
+        <v>2</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1654,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1187665708</t>
+          <t>1051850286</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187665708</t>
+          <t>https://m.place.naver.com/place/1051850286</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1770,29 +1774,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>초록뷰티</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>8852561@naver.com</t>
-        </is>
-      </c>
+          <t>하얀네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1496-1644</t>
+          <t>0507-1490-1110</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 883 상가 10동 2층 206호</t>
+          <t>부산광역시 사상구 동주로 24 1층 하얀네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chorok__beauty?igsh=Zm1vNDRnNHRueXJ6&amp;utm_source=qr</t>
+          <t>http://instagram.com/hayan_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1679896666</t>
+          <t>1581947459</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679896666</t>
+          <t>https://m.place.naver.com/place/1581947459</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1864,29 +1864,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>모라네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>jessicanail@naver.com</t>
-        </is>
-      </c>
+          <t>네일하이디</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1379-0989</t>
+          <t>0507-1341-4976</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로51번길 16 1층(모라네일)/구 헤이진 네일</t>
+          <t>부산광역시 사상구 백양대로504번길 2 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/heyjin2019</t>
+          <t>https://www.instagram.com/nail_hi.d</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1921,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1537116650</t>
+          <t>1061733115</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537116650</t>
+          <t>https://m.place.naver.com/place/1061733115</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1958,25 +1954,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
+          <t>일루아네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ggaau0073@naver.com</t>
+          <t>chltnwl900@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1497-8287</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 91 3층</t>
+          <t>부산광역시 사상구 엄궁북로 40 롯데캐슬상가 1동 104호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jbeauty_nailsalon?igsh=NG5ubXc0MjdocWMx&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/illua_suji</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2026,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2006084959</t>
+          <t>613016122</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006084959</t>
+          <t>https://m.place.naver.com/place/613016122</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2048,29 +2048,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>수아한네일</t>
+          <t>네일k</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ksh_6563@naver.com</t>
+          <t>oio7845@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1441-0277</t>
+          <t>0507-1313-2205</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 2층 248호</t>
+          <t>부산광역시 사상구 백양대로 490 주례1차동일아파트 106동 1층 107-2호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/suahan_nail?igsh=MTZnYnRmNmFnNTQ4MA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2120,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1798118492</t>
+          <t>1029204849</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798118492</t>
+          <t>https://m.place.naver.com/place/1029204849</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2142,29 +2142,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>예블링네일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>thsghkwlsas@naver.com</t>
-        </is>
-      </c>
+          <t>쏭네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1462-0158</t>
+          <t>0507-1355-9745</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 덕상로 19-1 1층 예블링네일</t>
+          <t>부산광역시 사상구 양지로24번길 2 1층 쏭네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yebling_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2174,7 +2170,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2195,17 +2191,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1115413707</t>
+          <t>1669157044</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115413707</t>
+          <t>https://m.place.naver.com/place/1669157044</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2236,25 +2232,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>홍네일</t>
+          <t>핸드네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6569807@naver.com</t>
+          <t>jessicanail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1379-4125</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로309번길 49</t>
+          <t>부산광역시 사상구 백양대로 916 우성아파트 상가1동 111호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jessicanail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>368</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2304,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1603273526</t>
+          <t>32794875</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1603273526</t>
+          <t>https://m.place.naver.com/place/32794875</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2326,29 +2326,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>빛날희네일</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>kimmihee4@naver.com</t>
-        </is>
-      </c>
+          <t>지혜네일샵</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1358-0304</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로104번길 27</t>
+          <t>부산광역시 사상구 삼덕로46번안길 28 조선사</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail03</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2358,7 +2350,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2379,17 +2371,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2390,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1358743723</t>
+          <t>1658577122</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358743723</t>
+          <t>https://m.place.naver.com/place/1658577122</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2412,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>준,네일</t>
+          <t>라움네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>noblelizent@naver.com</t>
+          <t>imraina@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1353-4384</t>
+          <t>0507-1361-9872</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁남로11번길 16 1층</t>
+          <t>부산광역시 사상구 사상로 166 리치플러스아파트 상가동 102호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/june__nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2452,7 +2444,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2473,17 +2465,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2484,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1490919782</t>
+          <t>1322569547</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490919782</t>
+          <t>https://m.place.naver.com/place/1322569547</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,30 +2506,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>눈부시네.일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>happygirlmh@naver.com</t>
-        </is>
-      </c>
+          <t>지니네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로9번길 3 눈부시네.일</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자상가 2층 273호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://toss-order.tossplace.com/booking/N2L40xfR9x2ivsY</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2563,17 +2551,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2570,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2145722253</t>
+          <t>31505917</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2145722253</t>
+          <t>https://m.place.naver.com/place/31505917</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2604,29 +2592,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>클라라네일</t>
+          <t>네일도설렘 부산점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>laura1016@naver.com</t>
+          <t>pongx22@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1352-5400</t>
+          <t>0507-1375-6752</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1401호</t>
+          <t>부산광역시 사상구 사상로 248 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sun.young218700</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2636,7 +2624,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2657,17 +2645,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>352</v>
+        <v>28</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2664,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>37638497</t>
+          <t>1809754813</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37638497</t>
+          <t>https://m.place.naver.com/place/1809754813</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2686,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네리나네일앤뷰티</t>
+          <t>샤네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kjinsook2004@naver.com</t>
+          <t>wood1030@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1428-1560</t>
+          <t>0507-1313-5869</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 강선로 18 1층 네리나 네일&amp;뷰티</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자상가 1층114호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nerina_nail?igsh=MXhiZ296NXdneXcw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/wood1030</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2735,7 +2723,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2755,13 +2743,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2758,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1273947079</t>
+          <t>33399488</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273947079</t>
+          <t>https://m.place.naver.com/place/33399488</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,34 +2780,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>오브네일</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ofrang@naver.com</t>
-        </is>
-      </c>
+          <t>예쁜손톱방</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1370-9776</t>
+          <t>0507-1337-2616</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로366번길 19 . 1층</t>
+          <t>부산광역시 사상구 학감대로 109-14 상가동 1층 101호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gxixiTG</t>
+          <t>http://www.instagram.com/yebbeun_nail_bang</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2840,7 +2824,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2849,13 +2833,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2848,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1071928305</t>
+          <t>1237764066</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071928305</t>
+          <t>https://m.place.naver.com/place/1237764066</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2870,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>두손네일</t>
+          <t>꿈꾸는네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>doosonnail@naver.com</t>
+          <t>dreamnail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1345-9948</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 8 두손네일</t>
+          <t>부산광역시 사상구 엄궁로179번길 9-8 꿈꾸는네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/doson_nail_jina</t>
+          <t>https://www.instagram.com/the_dream.nail</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2943,13 +2923,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1568106556</t>
+          <t>1792266910</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568106556</t>
+          <t>https://m.place.naver.com/place/1792266910</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2980,29 +2960,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일해찌</t>
+          <t>맑은네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>archive_olivia@naver.com</t>
+          <t>rhd0209@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1347-0019</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 172 A동 1층</t>
+          <t>부산광역시 사상구 대동로 106 목화아파트상가 3층 310호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhaejji_</t>
+          <t>http://instagram.com/malgeunnail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3037,13 +3013,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>391</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>432</v>
+        <v>24</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,17 +3028,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1433672492</t>
+          <t>1433389520</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433672492</t>
+          <t>https://m.place.naver.com/place/1433389520</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3074,34 +3050,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>핑크네일</t>
+          <t>레푸스 사상점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>go8282c@naver.com</t>
+          <t>mimongmnn@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1334-0020</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로 15 3층 핑크네일</t>
+          <t>부산광역시 사상구 사상로 208-1 10층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pinknail_busan</t>
+          <t>https://litt.ly/refuss_nail4season_busan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3131,13 +3103,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>15</v>
+        <v>676</v>
       </c>
       <c r="Q29" t="n">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="R29" t="n">
-        <v>347</v>
+        <v>836</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3118,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>36924982</t>
+          <t>1044773647</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36924982</t>
+          <t>https://m.place.naver.com/place/1044773647</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3168,29 +3140,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>thenail7282@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1399-0460</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 상가동 2층 282호</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼시떼관 1층 1396,1405호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/the_nail_sasang</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,7 +3168,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3221,17 +3189,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3208,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1060258369</t>
+          <t>1179834131</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060258369</t>
+          <t>https://m.place.naver.com/place/1179834131</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3230,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>모라네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>jessicanail@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3275,12 +3243,12 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼시떼관 1층 1396,1405호</t>
+          <t>부산광역시 사상구 모라로51번길 16</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_nail_sasang</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3290,7 +3258,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3311,17 +3279,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3330,17 +3298,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1179834131</t>
+          <t>2143022752</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179834131</t>
+          <t>https://m.place.naver.com/place/2143022752</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3352,35 +3320,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>샛별네일아트</t>
+          <t>늘예쁨 네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>pig_malion_@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1356-6612</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 2동 236호 (학장동,반도프라자)</t>
+          <t>부산광역시 사상구 가야대로 369 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xlQmxnn</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3396,22 +3368,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3392,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1396422090</t>
+          <t>2079016042</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396422090</t>
+          <t>https://m.place.naver.com/place/2079016042</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3442,29 +3414,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>힐링네일</t>
+          <t>클라라네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lovekeiti@naver.com</t>
+          <t>laura1016@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1423-9082</t>
+          <t>0507-1352-5400</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 384 1층 네일샵</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1층 1401호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_healing_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3474,7 +3446,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3495,17 +3467,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="R33" t="n">
-        <v>58</v>
+        <v>352</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3486,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2067519657</t>
+          <t>37638497</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067519657</t>
+          <t>https://m.place.naver.com/place/37638497</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3513,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ekgnlzz@naver.com</t>
+          <t>nailtoctoc@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3618,7 +3590,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3630,25 +3602,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일미</t>
+          <t>네일더예쁜눈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>041nail@naver.com</t>
+          <t>soojinpo@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1348-1127</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모덕로 32</t>
+          <t>부산광역시 사상구 가야대로366번길 56 2층 네일더예쁜눈</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://naileye.itpage.kr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3658,7 +3634,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3679,17 +3655,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3698,17 +3674,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1163149926</t>
+          <t>1141282133</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163149926</t>
+          <t>https://m.place.naver.com/place/1141282133</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3723,11 +3699,7 @@
           <t>네일공간</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>gol2006@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3802,7 +3774,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3814,29 +3786,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일1one</t>
+          <t>네일애 푸스케어 부산엄궁점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>high0902@naver.com</t>
+          <t>fusscare_nailaee@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1371-1157</t>
+          <t>0507-1379-0163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로1210번길 50 상가 동원부동산옆</t>
+          <t>부산광역시 사상구 엄궁로 144 1층 105호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail1one</t>
+          <t>https://www.instagram.com/nail.aee</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3871,13 +3843,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3886,17 +3858,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1150830105</t>
+          <t>1438869369</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150830105</t>
+          <t>https://m.place.naver.com/place/1438869369</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3908,29 +3880,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>주네일</t>
+          <t>로코네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jinrose22@naver.com</t>
+          <t>u_love118@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1406-7510</t>
+          <t>0507-1391-7108</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 28 1층 주네일</t>
+          <t>부산광역시 사상구 사상로238번길 5 . 1층 루니움뷰티&amp;케어</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/7junail7</t>
+          <t>https://www.instagram.com/_loconail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3956,7 +3928,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3965,13 +3937,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>257</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R38" t="n">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3980,17 +3952,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1705139517</t>
+          <t>1303113106</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1705139517</t>
+          <t>https://m.place.naver.com/place/1303113106</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4002,25 +3974,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>미유네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>atsing427@naver.com</t>
-        </is>
-      </c>
+          <t>주네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1406-7510</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로233번길 14 1층 102호</t>
+          <t>부산광역시 사상구 사상로238번길 28 1층 주네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/stxAgifc</t>
+          <t>https://www.instagram.com/7junail7</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4046,7 +4018,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4055,13 +4027,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4070,17 +4042,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2007447861</t>
+          <t>1705139517</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007447861</t>
+          <t>https://m.place.naver.com/place/1705139517</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4092,29 +4064,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일더예쁜눈</t>
+          <t>모라네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>soojinpo@naver.com</t>
+          <t>jessicanail@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1348-1127</t>
+          <t>0507-1379-0989</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로366번길 56 2층 네일더예쁜눈</t>
+          <t>부산광역시 사상구 모라로51번길 16 1층(모라네일)/구 헤이진 네일</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://naileye.itpage.kr</t>
+          <t>http://www.instagram.com/heyjin2019</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4149,13 +4121,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Q40" t="n">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="R40" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4164,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1141282133</t>
+          <t>1537116650</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141282133</t>
+          <t>https://m.place.naver.com/place/1537116650</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4186,29 +4158,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>라움네일</t>
+          <t>네일파크</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>realbarbie77@naver.com</t>
+          <t>eunmijan@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1361-9872</t>
+          <t>0507-1441-4147</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 166 리치플러스아파트 상가동 102호</t>
+          <t>부산광역시 사상구 가야대로360번길 1 2층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nailpark</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4218,7 +4190,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4239,17 +4211,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
-        <v>8</v>
+        <v>148</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4258,17 +4230,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1322569547</t>
+          <t>1218794769</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322569547</t>
+          <t>https://m.place.naver.com/place/1218794769</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4280,20 +4252,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>요술손</t>
+          <t>케이뷰티</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>yosulson_party@naver.com</t>
+          <t>bi1142@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>051-669-6355</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로250번길 22</t>
+          <t>부산광역시 사상구 낙동대로 910</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4333,13 +4309,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4348,17 +4324,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1330709122</t>
+          <t>1104145262</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330709122</t>
+          <t>https://m.place.naver.com/place/1104145262</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4370,35 +4346,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pickynail</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>라비앙로즈네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>daily__oe@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1333-5263</t>
+          <t>0507-1340-8327</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로223번길 23 303동 102호</t>
+          <t>부산광역시 사상구 가야대로 288 창조센츄리 상가 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_CZBEs</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4414,22 +4394,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4438,17 +4418,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2053102298</t>
+          <t>1335031344</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2053102298</t>
+          <t>https://m.place.naver.com/place/1335031344</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4460,29 +4440,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>하얀네일</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>whitenail27@naver.com</t>
-        </is>
-      </c>
+          <t>엄궁네일언니</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1490-1110</t>
+          <t>0507-1414-0567</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 동주로 24 1층 하얀네일</t>
+          <t>부산광역시 사상구 대동로 62 1층 네일언니</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/hayan_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4492,7 +4468,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4513,17 +4489,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4532,17 +4508,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1581947459</t>
+          <t>1607040684</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581947459</t>
+          <t>https://m.place.naver.com/place/1607040684</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4554,29 +4530,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일도설렘 부산점</t>
+          <t>아마폴라뷰티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>pongx22@naver.com</t>
+          <t>amapola3221016@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1375-6752</t>
+          <t>0507-1325-2164</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 248 2층</t>
+          <t>부산광역시 사상구 대동로 133-2 2층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sun.young218700</t>
+          <t>https://www.instagram.com/amapola_official_</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4611,13 +4587,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R45" t="n">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4626,17 +4602,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1809754813</t>
+          <t>1049170292</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809754813</t>
+          <t>https://m.place.naver.com/place/1049170292</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4648,29 +4624,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일&amp;풋</t>
+          <t>단미뷰티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>algid1235@naver.com</t>
+          <t>kmlove123@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1479-7850</t>
+          <t>0507-1390-0815</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 76 상가동 1층 104호</t>
+          <t>부산광역시 사상구 모라로110번길 5 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.and.foot</t>
+          <t>https://www.instagram.com/danmi__bt/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4705,13 +4681,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4720,17 +4696,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1395529953</t>
+          <t>1759913260</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395529953</t>
+          <t>https://m.place.naver.com/place/1759913260</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4742,29 +4718,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>용이뷰티</t>
+          <t>라니뷰티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>yurim012@naver.com</t>
+          <t>amore_rani@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1406-6990</t>
+          <t>0507-1382-0261</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 950</t>
+          <t>부산광역시 사상구 백양대로 998-1 2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_r._an._i._</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4774,7 +4750,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4795,17 +4771,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4814,17 +4790,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>38521099</t>
+          <t>1178399753</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38521099</t>
+          <t>https://m.place.naver.com/place/1178399753</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4836,24 +4812,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>퀸네일</t>
+          <t>요술손</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>miinijk@naver.com</t>
+          <t>yosulson_party@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1380-2805</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자 1층 110호 퀸네일</t>
+          <t>부산광역시 사상구 사상로250번길 22</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4893,13 +4865,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4908,17 +4880,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1679312982</t>
+          <t>1330709122</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679312982</t>
+          <t>https://m.place.naver.com/place/1330709122</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4930,39 +4902,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일콩</t>
+          <t>이쁘네.일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>besmlsk@naver.com</t>
+          <t>haennyo7997@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1306-3190</t>
+          <t>0507-1438-2541</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 덕상로 10 오양상가 303호 네일콩</t>
+          <t>부산광역시 사상구 가야대로 295 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailkong.k</t>
+          <t>http://이쁘네일.kr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4987,13 +4959,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R49" t="n">
-        <v>13</v>
+        <v>203</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5002,17 +4974,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1444223522</t>
+          <t>1106172366</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444223522</t>
+          <t>https://m.place.naver.com/place/1106172366</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5024,29 +4996,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>샤네일</t>
+          <t>힐링네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wood1030@naver.com</t>
+          <t>lovekeiti@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1313-5869</t>
+          <t>0507-1423-9082</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자상가 1층114호</t>
+          <t>부산광역시 사상구 가야대로 384 1층 네일샵</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wood1030</t>
+          <t>https://www.instagram.com/_healing_nail_</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5061,7 +5033,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5081,13 +5053,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5096,17 +5068,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>33399488</t>
+          <t>2067519657</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33399488</t>
+          <t>https://m.place.naver.com/place/2067519657</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5118,29 +5090,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일하루 사상본점</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>nolmukzzang@naver.com</t>
-        </is>
-      </c>
+          <t>네일포레</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1311-3336</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 214 3층 네일하루</t>
+          <t>부산광역시 사상구 사상로90번길 6 1층 왼쪽</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailharu3</t>
+          <t>https://www.instagram.com/nail_for.et?igsh=Zjk2cnE5emQ4MDR1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5175,13 +5139,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>831</v>
+        <v>2</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,17 +5154,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1328657179</t>
+          <t>2032419101</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328657179</t>
+          <t>https://m.place.naver.com/place/2032419101</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5212,29 +5176,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>달처럼예뻐라</t>
+          <t>네일하랑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>haru_04@naver.com</t>
+          <t>harang9488@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1494-2578</t>
+          <t>0507-1466-1336</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 28 상가13동 2층 205호</t>
+          <t>부산광역시 사상구 광장로 54 포르투나더테라스 2층 210호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail__ha_rang</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5244,7 +5208,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5260,22 +5224,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R52" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5284,17 +5248,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1699052156</t>
+          <t>1454851530</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699052156</t>
+          <t>https://m.place.naver.com/place/1454851530</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5306,24 +5270,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>쏭네일</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ssongnail01@naver.com</t>
-        </is>
-      </c>
+          <t>네일미</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1355-9745</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 양지로24번길 2 1층 쏭네일</t>
+          <t>부산광역시 사상구 모덕로 32</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5363,13 +5319,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5378,17 +5334,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1669157044</t>
+          <t>1163149926</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669157044</t>
+          <t>https://m.place.naver.com/place/1163149926</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5400,29 +5356,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일이지</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>rlathdms96@naver.com</t>
-        </is>
-      </c>
+          <t>썸네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1390-3978</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번가길 17-9 1층</t>
+          <t>부산광역시 사상구 엄궁북로 59 롯데캐슬리버 401동앞 상가1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_2ji</t>
+          <t>https://www.instagram.com/thumb__nail__?igshid=16cyosojl8iua</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5457,13 +5405,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5472,17 +5420,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2022406101</t>
+          <t>1022811581</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022406101</t>
+          <t>https://m.place.naver.com/place/1022811581</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5494,29 +5442,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아마폴라뷰티</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>amapola3221016@naver.com</t>
-        </is>
-      </c>
+          <t>무이네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1325-2164</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 133-2 2층</t>
+          <t>부산광역시 사상구 운산로 21 1층 (부산광역시 사상구 삼락동 418-8 1층)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/amapola_official_</t>
+          <t>https://www.instagram.com/mooinail_uz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5551,13 +5491,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5566,17 +5506,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1049170292</t>
+          <t>1347978558</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049170292</t>
+          <t>https://m.place.naver.com/place/1347978558</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5588,29 +5528,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일파크</t>
+          <t>용이뷰티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>eunmijan@naver.com</t>
+          <t>yurim012@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1441-4147</t>
+          <t>0507-1406-6990</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로360번길 1 2층</t>
+          <t>부산광역시 사상구 백양대로 950</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailpark</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5620,7 +5560,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5641,17 +5581,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5660,17 +5600,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1218794769</t>
+          <t>38521099</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218794769</t>
+          <t>https://m.place.naver.com/place/38521099</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5682,29 +5622,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일썸</t>
+          <t>쏭네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>un6ee@naver.com</t>
+          <t>ssongnail01@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1323-7075</t>
+          <t>0507-1372-6483</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로212번길 38 2층</t>
+          <t>부산광역시 사상구 낙동대로776번길 36 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.some_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5714,7 +5654,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5735,18 +5675,18 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
         <v>7</v>
       </c>
-      <c r="R57" t="n">
-        <v>40</v>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>X</t>
@@ -5754,17 +5694,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2052010949</t>
+          <t>1484173928</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052010949</t>
+          <t>https://m.place.naver.com/place/1484173928</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5776,39 +5716,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>이쁘네.일</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>haennyo7997@naver.com</t>
-        </is>
-      </c>
+          <t>네일도로시</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1438-2541</t>
+          <t>0507-1316-9113</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 295 1층</t>
+          <t>부산광역시 사상구 엄궁로203번길 38 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://이쁘네일.kr</t>
+          <t>https://instagram.com/_nail_dorothy_?igshid=irihcx1mq6ow</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5833,13 +5769,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,17 +5784,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1106172366</t>
+          <t>1033126412</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106172366</t>
+          <t>https://m.place.naver.com/place/1033126412</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5870,39 +5806,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제제네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>qnfnqnqn13@naver.com</t>
-        </is>
-      </c>
+          <t>채움네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1412-8079</t>
+          <t>0507-1392-7397</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로292번길 28 1층 JEJENAIL</t>
+          <t>부산광역시 사상구 백양대로 884 상가동 1층 121호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_KxbBEn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5918,22 +5850,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,17 +5874,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1926033569</t>
+          <t>1354678970</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926033569</t>
+          <t>https://m.place.naver.com/place/1354678970</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5964,39 +5896,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>라비앙로즈네일</t>
+          <t>샛별네일아트</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ogamza_@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1340-8327</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 288 창조센츄리 상가 2층</t>
+          <t>부산광역시 사상구 대동로 94 2동 236호 (학장동,반도프라자)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_CZBEs</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6012,22 +5940,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +5964,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1335031344</t>
+          <t>1396422090</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335031344</t>
+          <t>https://m.place.naver.com/place/1396422090</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6058,39 +5986,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일와요</t>
+          <t>TOAS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>shintc@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1364-2465</t>
+          <t>051-325-9903</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로223번길 23 서희센트럴스타힐스 106동 2층 204호</t>
+          <t>부산광역시 사상구 운산로 22</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NQdnG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6106,22 +6034,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,17 +6058,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1509491646</t>
+          <t>1997973035</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509491646</t>
+          <t>https://m.place.naver.com/place/1997973035</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6152,20 +6080,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>유유네일</t>
+          <t>유네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>thgus4613@naver.com</t>
+          <t>luvu1016@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1399-0460</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로306번길 79</t>
+          <t>부산광역시 사상구 대동로 94 상가동 2층 282호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6205,13 +6137,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6220,17 +6152,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37979962</t>
+          <t>1060258369</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37979962</t>
+          <t>https://m.place.naver.com/place/1060258369</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6242,29 +6174,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>퀸즈네일</t>
+          <t>썬뷰티네일샵</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>qu_eenz@naver.com</t>
+          <t>artst_snu@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>051-322-1145</t>
+          <t>0507-1375-2696</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 괘감로 97</t>
+          <t>부산광역시 사상구 백양대로342번길 21 206호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sunnailshop2696</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6274,7 +6206,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6295,17 +6227,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6314,17 +6246,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21505702</t>
+          <t>1498701306</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21505702</t>
+          <t>https://m.place.naver.com/place/1498701306</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6336,29 +6268,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>일루아네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>chltnwl900@naver.com</t>
-        </is>
-      </c>
+          <t>하이네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1497-8287</t>
+          <t>0507-1308-0940</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁북로 40 롯데캐슬상가 1동 104호</t>
+          <t>부산광역시 사상구 사상로342번길 21 벽산늘푸른상가 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/illua_suji</t>
+          <t>http://www.instagram.com/hi_nailll</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6393,13 +6321,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6408,17 +6336,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>613016122</t>
+          <t>1223881417</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/613016122</t>
+          <t>https://m.place.naver.com/place/1223881417</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6430,29 +6358,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네로뷰티</t>
+          <t>네일제이</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>nr08@naver.com</t>
+          <t>jiwon3716@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1316-7440</t>
+          <t>0507-1308-3976</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 974 2층 네로뷰티(진갈비 2층)</t>
+          <t>부산광역시 사상구 백양대로 326 1층 네일제이</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/shy5VQef</t>
+          <t>https://blog.naver.com/jiwon3716</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6467,7 +6395,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6478,7 +6406,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6487,13 +6415,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>286</v>
+        <v>51</v>
       </c>
       <c r="Q65" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R65" t="n">
-        <v>315</v>
+        <v>76</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6430,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1785862913</t>
+          <t>1944314268</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785862913</t>
+          <t>https://m.place.naver.com/place/1944314268</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6524,24 +6452,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>루미아 네일 뷰티케어</t>
+          <t>주강희 네일샵</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>pochun_ant@naver.com</t>
+          <t>overflow0409@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1345-8988</t>
+          <t>070-4413-4141</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로907번가길 54 1층</t>
+          <t>부산광역시 사상구 백양대로 884 우신모라아파트</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6581,13 +6509,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6524,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2095013714</t>
+          <t>1354914865</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095013714</t>
+          <t>https://m.place.naver.com/place/1354914865</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6618,29 +6546,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아이리스네일</t>
+          <t>초록뷰티</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kitty666@naver.com</t>
+          <t>8852561@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>051-319-5413</t>
+          <t>0507-1496-1644</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 시떼관 1413호</t>
+          <t>부산광역시 사상구 백양대로 883 상가 10동 2층 206호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kitty666</t>
+          <t>https://www.instagram.com/chorok__beauty?igsh=Zm1vNDRnNHRueXJ6&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6655,7 +6583,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6671,17 +6599,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6618,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>35228104</t>
+          <t>1679896666</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35228104</t>
+          <t>https://m.place.naver.com/place/1679896666</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6712,29 +6640,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일송송 사상점</t>
+          <t>루미아 네일 뷰티케어</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ssons_shop@naver.com</t>
+          <t>pochun_ant@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>051-303-7333</t>
+          <t>0507-1345-8988</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 712 남영아파트상가 2동 1층 8호</t>
+          <t>부산광역시 사상구 백양대로907번가길 54 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssons_shop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6744,12 +6672,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6765,17 +6693,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,17 +6712,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1824794292</t>
+          <t>2095013714</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824794292</t>
+          <t>https://m.place.naver.com/place/2095013714</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6806,20 +6734,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>마녀손톱</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>vitaminiya@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>051-311-2204</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도상가 2층 238호</t>
+          <t>부산광역시 사상구 백양대로494번길 19</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6859,13 +6791,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6874,17 +6806,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2027108055</t>
+          <t>1020368554</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027108055</t>
+          <t>https://m.place.naver.com/place/1020368554</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6896,29 +6828,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>핸드네일</t>
+          <t>야시 속눈썹&amp;네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jessicanail@naver.com</t>
+          <t>nice0304011@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1379-4125</t>
+          <t>0507-1303-4262</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 916 우성아파트 상가1동 111호</t>
+          <t>부산광역시 사상구 사상로 484 1층 야시속눈썹</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jessicanail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6928,12 +6860,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6949,17 +6881,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>344</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>368</v>
+        <v>10</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6968,17 +6900,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>32794875</t>
+          <t>1656610719</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32794875</t>
+          <t>https://m.place.naver.com/place/1656610719</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6990,29 +6922,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>비쥬네일</t>
+          <t>네일마루&amp;카페</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h2425@naver.com</t>
+          <t>suji6777@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1447-8896</t>
+          <t>0507-1321-4724</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 새벽로 173</t>
+          <t>부산광역시 사상구 백양대로 372-22 반도보라메머드타운상가 209호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailmaru</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7022,7 +6954,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7043,17 +6975,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q71" t="n">
         <v>3</v>
       </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
       <c r="R71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7062,17 +6994,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1956450361</t>
+          <t>1730313997</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956450361</t>
+          <t>https://m.place.naver.com/place/1730313997</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7084,34 +7016,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일혜현</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>hyeon_2124@naver.com</t>
-        </is>
-      </c>
+          <t>너도,네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1306-1292</t>
+          <t>0507-1399-2081</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로97번길 46 1층</t>
+          <t>부산광역시 사상구 주례로9번길 83 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhxiPKK/chat</t>
+          <t>http://www.instagram.com/nido_nail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7132,7 +7060,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7141,13 +7069,13 @@
         </is>
       </c>
       <c r="P72" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>44</v>
-      </c>
       <c r="R72" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7156,17 +7084,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1925352608</t>
+          <t>1917089461</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925352608</t>
+          <t>https://m.place.naver.com/place/1917089461</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7178,29 +7106,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오라네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>wjsska1907@naver.com</t>
-        </is>
-      </c>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1361-8337</t>
+          <t>0507-1303-2195</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로1210번길 88</t>
+          <t>부산광역시 사상구 대동로 94 반도보라타운252호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_O_ranail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7210,7 +7134,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7231,17 +7155,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R73" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7250,17 +7174,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1910001099</t>
+          <t>1549283623</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910001099</t>
+          <t>https://m.place.naver.com/place/1549283623</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7272,34 +7196,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>포인트뷰티</t>
+          <t>23도네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>vjvmf_love@naver.com</t>
+          <t>dbcom36@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1344-0097</t>
+          <t>0507-1339-5124</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 양지로30번길 9 상가 2층</t>
+          <t>부산광역시 사상구 사상로233번길 16 1층 101호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_point_beauty</t>
+          <t>http://pf.kakao.com/_WaGxjxb</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7320,22 +7244,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>29</v>
+        <v>216</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="R74" t="n">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7268,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1699053374</t>
+          <t>1908955863</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699053374</t>
+          <t>https://m.place.naver.com/place/1908955863</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7366,34 +7290,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>가꾸다네일</t>
+          <t>미유네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>chl4550@naver.com</t>
+          <t>gmlwjd1902@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1439-1785</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 208-1 12층 1202호</t>
+          <t>부산광역시 사상구 사상로233번길 14 1층 102호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gakkuda_nail1</t>
+          <t>https://open.kakao.com/o/stxAgifc</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7414,7 +7334,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7426,10 +7346,10 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7358,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2009578695</t>
+          <t>2007447861</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009578695</t>
+          <t>https://m.place.naver.com/place/2007447861</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7380,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일하는언니</t>
+          <t>백아네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>cmk11273@naver.com</t>
+          <t>love_dlehdgo@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>051-987-7998</t>
+          <t>0507-1338-8558</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로342번길 37 블루밍@상가동1층103호</t>
+          <t>부산광역시 사상구 대동로 94 상가동 243호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailunnie_ja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7492,7 +7412,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7508,22 +7428,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,17 +7452,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1400451423</t>
+          <t>1180139663</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400451423</t>
+          <t>https://m.place.naver.com/place/1180139663</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7554,29 +7474,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일스토리</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>yeju0414@naver.com</t>
-        </is>
-      </c>
+          <t>옐블링</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1303-2195</t>
+          <t>0507-1347-4690</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도보라타운252호</t>
+          <t>부산광역시 사상구 사상로238번길 35 1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yelbling___</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7586,7 +7502,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7602,22 +7518,22 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7626,17 +7542,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1549283623</t>
+          <t>1434085437</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549283623</t>
+          <t>https://m.place.naver.com/place/1434085437</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7648,29 +7564,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>손블링네일</t>
+          <t>포인트뷰티</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>riplim@naver.com</t>
+          <t>vjvmf_love@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1377-2398</t>
+          <t>0507-1344-0097</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로306번길 79 1층 손블링네일</t>
+          <t>부산광역시 사상구 양지로30번길 9 상가 2층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sonbling_nail/</t>
+          <t>https://www.instagram.com/_point_beauty</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7705,13 +7621,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R78" t="n">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7720,17 +7636,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2007060512</t>
+          <t>1699053374</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007060512</t>
+          <t>https://m.place.naver.com/place/1699053374</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7742,24 +7658,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>백아네일</t>
+          <t>홍네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>love_dlehdgo@naver.com</t>
+          <t>6569807@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1338-8558</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 상가동 243호</t>
+          <t>부산광역시 사상구 사상로309번길 49</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7802,10 +7714,10 @@
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7814,17 +7726,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1180139663</t>
+          <t>1603273526</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180139663</t>
+          <t>https://m.place.naver.com/place/1603273526</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7836,29 +7748,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일도로시</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>whektha1613@naver.com</t>
-        </is>
-      </c>
+          <t>네일해찌</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1316-9113</t>
+          <t>0507-1347-0019</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로203번길 38 1층</t>
+          <t>부산광역시 사상구 사상로 172 A동 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://instagram.com/_nail_dorothy_?igshid=irihcx1mq6ow</t>
+          <t>https://www.instagram.com/nailhaejji_</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7893,13 +7801,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>392</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="R80" t="n">
-        <v>12</v>
+        <v>433</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7908,17 +7816,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1033126412</t>
+          <t>1433672492</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033126412</t>
+          <t>https://m.place.naver.com/place/1433672492</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7930,34 +7838,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>주네일</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>jinrose22@naver.com</t>
-        </is>
-      </c>
+          <t>썬네일</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1309-0526</t>
+          <t>0507-1356-6980</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로179번길 21 3층 주네일</t>
+          <t>부산광역시 사상구 광장로 7 1층 1번가 1337,1338호(괘법동, 르네시떼)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>http://instagram.com/joonail623</t>
+          <t>https://zero.gongbiz.kr/shop/S000016770</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7987,13 +7891,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8002,17 +7906,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1588835862</t>
+          <t>1046901734</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588835862</t>
+          <t>https://m.place.naver.com/place/1046901734</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8024,25 +7928,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>썸네일</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>hackerstalk11@naver.com</t>
-        </is>
-      </c>
+          <t>네일썸</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1323-7075</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁북로 59 롯데캐슬리버 401동앞 상가1층</t>
+          <t>부산광역시 사상구 사상로212번길 38 2층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thumb__nail__?igshid=16cyosojl8iua</t>
+          <t>https://www.instagram.com/nail.some_</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8077,13 +7981,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="Q82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R82" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8092,17 +7996,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1022811581</t>
+          <t>2052010949</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022811581</t>
+          <t>https://m.place.naver.com/place/2052010949</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8114,25 +8018,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일포레</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>nail_foret@naver.com</t>
-        </is>
-      </c>
+          <t>수아한네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1441-0277</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로90번길 6 1층 왼쪽</t>
+          <t>부산광역시 사상구 대동로 94 2층 248호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_for.et?igsh=Zjk2cnE5emQ4MDR1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/suahan_nail?igsh=MTZnYnRmNmFnNTQ4MA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8167,13 +8071,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8182,17 +8086,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2032419101</t>
+          <t>1798118492</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032419101</t>
+          <t>https://m.place.naver.com/place/1798118492</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8204,29 +8108,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>예쁜손톱방</t>
+          <t>주네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>hina_lanayahgas@naver.com</t>
+          <t>jinrose22@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1337-2616</t>
+          <t>0507-1309-0526</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로 109-14 상가동 1층 101호</t>
+          <t>부산광역시 사상구 엄궁로179번길 21 3층 주네일</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yebbeun_nail_bang</t>
+          <t>http://instagram.com/joonail623</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8261,13 +8165,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8276,17 +8180,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1237764066</t>
+          <t>1588835862</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237764066</t>
+          <t>https://m.place.naver.com/place/1588835862</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8298,29 +8202,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>너도,네일</t>
+          <t>네일송송 사상점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>ssons_shop@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1399-2081</t>
+          <t>051-303-7333</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로9번길 83 1층</t>
+          <t>부산광역시 사상구 백양대로 712 남영아파트상가 2동 1층 8호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nido_nail</t>
+          <t>https://blog.naver.com/ssons_shop</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8335,7 +8239,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8355,13 +8259,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="R85" t="n">
-        <v>19</v>
+        <v>501</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8370,17 +8274,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1917089461</t>
+          <t>1824794292</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917089461</t>
+          <t>https://m.place.naver.com/place/1824794292</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8392,25 +8296,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>맑은네일</t>
+          <t>핑크네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rhd0209@naver.com</t>
+          <t>go8282c@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1334-0020</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 106 목화아파트상가 3층 310호</t>
+          <t>부산광역시 사상구 주례로 15 3층 핑크네일</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://instagram.com/malgeunnail</t>
+          <t>https://www.instagram.com/pinknail_busan</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8445,13 +8353,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q86" t="n">
-        <v>22</v>
+        <v>332</v>
       </c>
       <c r="R86" t="n">
-        <v>24</v>
+        <v>347</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8460,17 +8368,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1433389520</t>
+          <t>36924982</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433389520</t>
+          <t>https://m.place.naver.com/place/36924982</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8482,29 +8390,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>라니뷰티</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>amore_rani@naver.com</t>
-        </is>
-      </c>
+          <t>퀸즈네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1382-0261</t>
+          <t>051-322-1145</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 998-1 2층</t>
+          <t>부산광역시 사상구 괘감로 97</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://instagram.com/_r._an._i._</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8514,7 +8418,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8535,17 +8439,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8554,17 +8458,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1178399753</t>
+          <t>21505702</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178399753</t>
+          <t>https://m.place.naver.com/place/21505702</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8576,39 +8480,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>엄궁네일언니</t>
+          <t>네일혜현</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>22hansol22@naver.com</t>
+          <t>hyeon_2124@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1414-0567</t>
+          <t>0507-1306-1292</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 62 1층 네일언니</t>
+          <t>부산광역시 사상구 광장로97번길 46 1층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhxiPKK/chat</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8624,22 +8528,22 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R88" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8648,17 +8552,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1607040684</t>
+          <t>1925352608</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1607040684</t>
+          <t>https://m.place.naver.com/place/1925352608</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8670,29 +8574,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>네일1one</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>high0902@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>051-315-1007</t>
+          <t>0507-1371-1157</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 774-1</t>
+          <t>부산광역시 사상구 낙동대로1210번길 50 상가 동원부동산옆</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_grimi</t>
+          <t>http://instagram.com/nail1one</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8727,13 +8631,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8742,17 +8646,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1051850286</t>
+          <t>1150830105</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051850286</t>
+          <t>https://m.place.naver.com/place/1150830105</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8764,29 +8668,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>로코네일</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>u_love118@naver.com</t>
-        </is>
-      </c>
+          <t>네일블라썸</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1391-7108</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 5 . 1층 루니움뷰티&amp;케어</t>
+          <t>부산광역시 사상구 대동로 94 반도상가 2층 238호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_loconail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8796,7 +8692,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8812,22 +8708,22 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8836,17 +8732,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1303113106</t>
+          <t>2027108055</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303113106</t>
+          <t>https://m.place.naver.com/place/2027108055</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8858,39 +8754,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일하랑</t>
+          <t>눈부시네.일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>harang9488@naver.com</t>
+          <t>happygirlmh@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1466-1336</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 54 포르투나더테라스 2층 210호</t>
+          <t>부산광역시 사상구 주례로9번길 3 눈부시네.일</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__ha_rang</t>
+          <t>https://toss-order.tossplace.com/booking/N2L40xfR9x2ivsY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8906,7 +8798,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8915,13 +8807,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="Q91" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8930,17 +8822,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1454851530</t>
+          <t>2145722253</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454851530</t>
+          <t>https://m.place.naver.com/place/2145722253</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8952,29 +8844,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>네일하이디</t>
+          <t>손블링네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>smwls0114@naver.com</t>
+          <t>sunnie0815@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1341-4976</t>
+          <t>0507-1377-2398</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로504번길 2 1층</t>
+          <t>부산광역시 사상구 가야대로306번길 79 1층 손블링네일</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hi.d</t>
+          <t>https://www.instagram.com/sonbling_nail/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9009,13 +8901,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="Q92" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R92" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9024,17 +8916,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1061733115</t>
+          <t>2007060512</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061733115</t>
+          <t>https://m.place.naver.com/place/2007060512</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9046,29 +8938,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일더드림</t>
+          <t>오라네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>rabbit0577@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>051-323-0807</t>
+          <t>0507-1361-8337</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 195</t>
+          <t>부산광역시 사상구 낙동대로1210번길 88</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thedream/</t>
+          <t>http://www.instagram.com/_O_ranail</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9103,13 +8995,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9118,17 +9010,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>517958118</t>
+          <t>1910001099</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/517958118</t>
+          <t>https://m.place.naver.com/place/1910001099</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9140,29 +9032,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>하이네일</t>
+          <t>빛날희네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>dojulie@naver.com</t>
+          <t>kimmihee4@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1308-0940</t>
+          <t>0507-1358-0304</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로342번길 21 벽산늘푸른상가 2층</t>
+          <t>부산광역시 사상구 광장로104번길 27</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hi_nailll</t>
+          <t>https://www.instagram.com/heenail03</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9197,13 +9089,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q94" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9212,17 +9104,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1223881417</t>
+          <t>1358743723</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223881417</t>
+          <t>https://m.place.naver.com/place/1358743723</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9234,34 +9126,34 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>네일마루&amp;카페</t>
+          <t>제제네일</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>suji6777@naver.com</t>
+          <t>qnfnqnqn13@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1321-4724</t>
+          <t>0507-1412-8079</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 372-22 반도보라메머드타운상가 209호</t>
+          <t>부산광역시 사상구 사상로292번길 28 1층 JEJENAIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailmaru</t>
+          <t>https://pf.kakao.com/_KxbBEn</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9282,7 +9174,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9291,13 +9183,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R95" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9306,17 +9198,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1730313997</t>
+          <t>1926033569</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730313997</t>
+          <t>https://m.place.naver.com/place/1926033569</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9328,29 +9220,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>씨네일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ansh1128@naver.com</t>
-        </is>
-      </c>
+          <t>pickynail</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1382-8160</t>
+          <t>0507-1333-5263</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 733 롯데마트 사상점 3층</t>
+          <t>부산광역시 사상구 사상로223번길 23 303동 102호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/cnail_3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9360,7 +9248,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9381,17 +9269,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9400,17 +9288,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>16801995</t>
+          <t>2053102298</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16801995</t>
+          <t>https://m.place.naver.com/place/2053102298</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9422,34 +9310,34 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>옐블링</t>
+          <t>네일와요</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>kkonge_@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1347-4690</t>
+          <t>0507-1364-2465</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로238번길 35 1층</t>
+          <t>부산광역시 사상구 사상로223번길 23 서희센트럴스타힐스 106동 2층 204호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yelbling___</t>
+          <t>https://pf.kakao.com/_NQdnG</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9479,13 +9367,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R97" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9494,17 +9382,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1434085437</t>
+          <t>1509491646</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434085437</t>
+          <t>https://m.place.naver.com/place/1509491646</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9516,34 +9404,34 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>이상한나라뷰티</t>
+          <t>네일콩</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ria2101@naver.com</t>
+          <t>besmlsk@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1373-2406</t>
+          <t>0507-1306-3190</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로37번길 84 1층</t>
+          <t>부산광역시 사상구 덕상로 10 오양상가 303호 네일콩</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tauxcG</t>
+          <t>https://www.instagram.com/nailkong.k</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9564,7 +9452,7 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9573,13 +9461,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9588,17 +9476,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1451827533</t>
+          <t>1444223522</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451827533</t>
+          <t>https://m.place.naver.com/place/1444223522</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9610,29 +9498,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HERO 네일</t>
+          <t>비쥬네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>hero_0304@naver.com</t>
+          <t>a8365435@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1368-2076</t>
+          <t>0507-1447-8896</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 760 1층</t>
+          <t>부산광역시 사상구 새벽로 173</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hero_nail_1101</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9642,7 +9530,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9663,17 +9551,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9682,17 +9570,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1884120549</t>
+          <t>1956450361</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884120549</t>
+          <t>https://m.place.naver.com/place/1956450361</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9704,29 +9592,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>단미뷰티</t>
+          <t>네일더끌림</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>kmlove123@naver.com</t>
+          <t>rktngpfud@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1390-0815</t>
+          <t>051-977-0977</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로110번길 5 2층</t>
+          <t>부산광역시 사상구 운산로 47 네일더끌림</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danmi__bt/</t>
+          <t>https://blog.naver.com/rktngpfud</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9741,7 +9629,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9761,13 +9649,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R100" t="n">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9776,17 +9664,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1759913260</t>
+          <t>1805551094</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759913260</t>
+          <t>https://m.place.naver.com/place/1805551094</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9798,29 +9686,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>뚜디살롱</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>lliii99966@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1392-7397</t>
+          <t>0507-1468-8936</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 884 상가동 1층 121호</t>
+          <t>부산광역시 사상구 가야대로284번길 2 럭키종합상가 18동 1층 8호</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ddudi_salon</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9830,7 +9718,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9851,17 +9739,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9870,17 +9758,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1354678970</t>
+          <t>1682930248</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354678970</t>
+          <t>https://m.place.naver.com/place/1682930248</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9892,25 +9780,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>무이네일</t>
+          <t>가꾸다네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>baeyou0417@naver.com</t>
+          <t>chl4550@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1439-1785</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 21 1층 (부산광역시 사상구 삼락동 418-8 1층)</t>
+          <t>부산광역시 사상구 사상로 208-1 12층 1202호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mooinail_uz</t>
+          <t>https://www.instagram.com/gakkuda_nail1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9945,13 +9837,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9960,17 +9852,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1347978558</t>
+          <t>2009578695</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347978558</t>
+          <t>https://m.place.naver.com/place/2009578695</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9982,29 +9874,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>네일k</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>oio7845@naver.com</t>
-        </is>
-      </c>
+          <t>숲,Nail Studio</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1313-2205</t>
+          <t>0507-1389-2939</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 490 주례1차동일아파트 106동 1층 107-2호</t>
+          <t>부산광역시 사상구 모라로88번길 17 1층</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/soopnail_</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10014,7 +9902,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10035,17 +9923,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10054,17 +9942,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1029204849</t>
+          <t>1882913328</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1029204849</t>
+          <t>https://m.place.naver.com/place/1882913328</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10076,29 +9964,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TOAS</t>
+          <t>두손네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>shintc@naver.com</t>
+          <t>doosonnail@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>051-325-9903</t>
+          <t>0507-1345-9948</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 22</t>
+          <t>부산광역시 사상구 사상로238번길 8 두손네일</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/doson_nail_jina</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10108,7 +9996,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10129,17 +10017,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10148,17 +10036,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1997973035</t>
+          <t>1568106556</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997973035</t>
+          <t>https://m.place.naver.com/place/1568106556</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10170,39 +10058,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>슈가네일</t>
+          <t>오브네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>junge1004j@naver.com</t>
+          <t>capcue@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>051-316-4145</t>
+          <t>0507-1370-9776</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 288</t>
+          <t>부산광역시 사상구 가야대로366번길 19 . 1층</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_gxixiTG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10218,22 +10106,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R105" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10242,17 +10130,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1626070548</t>
+          <t>1071928305</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626070548</t>
+          <t>https://m.place.naver.com/place/1071928305</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10264,29 +10152,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>손톱공주</t>
+          <t>네일이지</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ha___60@naver.com</t>
+          <t>juaefeel@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>051-321-0453</t>
+          <t>0507-1390-3978</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 98</t>
+          <t>부산광역시 사상구 엄궁로179번가길 17-9 1층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_2ji</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10296,7 +10184,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10317,17 +10205,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10336,17 +10224,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>38412266</t>
+          <t>2022406101</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38412266</t>
+          <t>https://m.place.naver.com/place/2022406101</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10358,29 +10246,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>야시 속눈썹&amp;네일</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>nice0304011@naver.com</t>
-        </is>
-      </c>
+          <t>씨네일</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1303-4262</t>
+          <t>0507-1382-8160</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 484 1층 야시속눈썹</t>
+          <t>부산광역시 사상구 낙동대로 733 롯데마트 사상점 3층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/cnail_3</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10390,7 +10274,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10411,17 +10295,17 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R107" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10430,17 +10314,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1656610719</t>
+          <t>16801995</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656610719</t>
+          <t>https://m.place.naver.com/place/16801995</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10452,29 +10336,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>주강희 네일샵</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>overflow0409@naver.com</t>
-        </is>
-      </c>
+          <t>준,네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>070-4413-4141</t>
+          <t>0507-1353-4384</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 884 우신모라아파트</t>
+          <t>부산광역시 사상구 엄궁남로11번길 16 1층</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/june__nail_/</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10484,7 +10364,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10505,17 +10385,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R108" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10524,17 +10404,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1354914865</t>
+          <t>1490919782</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354914865</t>
+          <t>https://m.place.naver.com/place/1490919782</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10546,29 +10426,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>23도네일</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>dbcom36@naver.com</t>
-        </is>
-      </c>
+          <t>이상한나라뷰티</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1339-5124</t>
+          <t>0507-1373-2406</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로233번길 16 1층 101호</t>
+          <t>부산광역시 사상구 광장로37번길 84 1층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WaGxjxb</t>
+          <t>http://pf.kakao.com/_tauxcG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10599,17 +10475,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="Q109" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10618,17 +10494,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1908955863</t>
+          <t>1451827533</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1908955863</t>
+          <t>https://m.place.naver.com/place/1451827533</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10640,29 +10516,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>뚜디살롱</t>
+          <t>유유네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>lliii99966@naver.com</t>
+          <t>thgus4613@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0507-1468-8936</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로284번길 2 럭키종합상가 18동 1층 8호</t>
+          <t>부산광역시 사상구 가야대로306번길 79</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ddudi_salon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10672,7 +10544,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10693,17 +10565,17 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="Q110" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>330</v>
+        <v>8</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10712,17 +10584,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1682930248</t>
+          <t>37979962</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682930248</t>
+          <t>https://m.place.naver.com/place/37979962</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10734,29 +10606,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일존 이마트사상점</t>
+          <t>네일로움 &amp; 속눈썹</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>marilov21@naver.com</t>
+          <t>vjkzmf10@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>051-710-6535</t>
+          <t>0507-1370-0917</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 17 이마트 사상점 1층</t>
+          <t>부산광역시 사상구 운산로 36 한신아파트1차 상가 2층 네일로움</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_nailroum_</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10766,7 +10638,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10787,17 +10659,17 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>15</v>
+        <v>301</v>
       </c>
       <c r="Q111" t="n">
-        <v>2</v>
+        <v>245</v>
       </c>
       <c r="R111" t="n">
-        <v>17</v>
+        <v>546</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10806,17 +10678,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>31229660</t>
+          <t>1187665708</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229660</t>
+          <t>https://m.place.naver.com/place/1187665708</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10828,25 +10700,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>레푸스 사상점</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>mimongmnn@naver.com</t>
-        </is>
-      </c>
+          <t>네로뷰티</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1316-7440</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 208-1 10층</t>
+          <t>부산광역시 사상구 백양대로 974 2층 네로뷰티(진갈비 2층)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://litt.ly/refuss_nail4season_busan</t>
+          <t>https://open.kakao.com/o/shy5VQef</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10872,7 +10744,7 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -10881,13 +10753,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>663</v>
+        <v>286</v>
       </c>
       <c r="Q112" t="n">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="R112" t="n">
-        <v>823</v>
+        <v>315</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10896,17 +10768,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1044773647</t>
+          <t>1785862913</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044773647</t>
+          <t>https://m.place.naver.com/place/1785862913</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10918,29 +10790,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>숲,Nail Studio</t>
+          <t>네일더드림</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>y_unjiv_v@naver.com</t>
+          <t>rabbit0577@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1389-2939</t>
+          <t>051-323-0807</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 모라로88번길 17 1층</t>
+          <t>부산광역시 사상구 엄궁로 195</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soopnail_</t>
+          <t>https://www.instagram.com/nail_thedream/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10975,13 +10847,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R113" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10990,17 +10862,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1882913328</t>
+          <t>517958118</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882913328</t>
+          <t>https://m.place.naver.com/place/517958118</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11012,29 +10884,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>손톱공주</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>tpgud7142@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1331-6537</t>
+          <t>051-321-0453</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 372-16 상가3층 제이제이네일</t>
+          <t>부산광역시 사상구 대동로 98</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>http://instagram.com/j.j__nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11044,7 +10916,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11065,17 +10937,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11084,17 +10956,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1221988261</t>
+          <t>38412266</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221988261</t>
+          <t>https://m.place.naver.com/place/38412266</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11106,29 +10978,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>네일더끌림</t>
+          <t>예블링네일</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>rktngpfud@naver.com</t>
+          <t>yevely66@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>051-977-0977</t>
+          <t>0507-1462-0158</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 47 네일더끌림</t>
+          <t>부산광역시 사상구 덕상로 19-1 1층 예블링네일</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rktngpfud</t>
+          <t>https://www.instagram.com/yebling_nail</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11143,7 +11015,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11163,13 +11035,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11178,17 +11050,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1805551094</t>
+          <t>1115413707</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805551094</t>
+          <t>https://m.place.naver.com/place/1115413707</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11200,34 +11072,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>늘예쁨 네일</t>
+          <t>네일&amp;풋</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>pig_malion_@naver.com</t>
+          <t>algid1235@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1356-6612</t>
+          <t>0507-1479-7850</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 369 1층</t>
+          <t>부산광역시 사상구 대동로 76 상가동 1층 104호</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlQmxnn</t>
+          <t>https://www.instagram.com/nail.and.foot</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11248,7 +11120,7 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -11257,13 +11129,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="Q116" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="R116" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11272,17 +11144,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>2079016042</t>
+          <t>1395529953</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079016042</t>
+          <t>https://m.place.naver.com/place/1395529953</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11248,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
